--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,48 +1063,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>334447</v>
+        <v>135350748</v>
       </c>
       <c r="B6" t="n">
-        <v>91923</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599140</v>
+        <v>599345</v>
       </c>
       <c r="R6" t="n">
-        <v>7330614</v>
+        <v>7330968</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1128,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,44 +1158,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>376098</v>
+        <v>334447</v>
       </c>
       <c r="B7" t="n">
-        <v>92369</v>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>385987</v>
+        <v>376098</v>
       </c>
       <c r="B8" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,32 +1368,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>520073</v>
+        <v>385987</v>
       </c>
       <c r="B9" t="n">
-        <v>92292</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>414990</v>
+        <v>520073</v>
       </c>
       <c r="B10" t="n">
-        <v>92097</v>
+        <v>92292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>1506</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,39 +1555,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1120620</v>
+        <v>414990</v>
       </c>
       <c r="B11" t="n">
-        <v>92632</v>
+        <v>92097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1886847</v>
+        <v>1120620</v>
       </c>
       <c r="B12" t="n">
-        <v>92333</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1670,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,17 +1749,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4043291</v>
+        <v>1886847</v>
       </c>
       <c r="B13" t="n">
-        <v>106229</v>
+        <v>92333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1767,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1836,6 +1850,436 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4043291</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135350592</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>864</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>600105</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7331205</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135350590</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92320</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>600137</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7331217</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135350592</v>
+        <v>135351898</v>
       </c>
       <c r="B15" t="n">
         <v>79452</v>
@@ -1981,17 +1981,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600105</v>
+        <v>600023</v>
       </c>
       <c r="R15" t="n">
-        <v>7331205</v>
+        <v>7331182</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2045,12 +2045,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2061,32 +2061,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135350590</v>
+        <v>135350592</v>
       </c>
       <c r="B16" t="n">
-        <v>92320</v>
+        <v>79452</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2063</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,13 +2096,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600137</v>
+        <v>600105</v>
       </c>
       <c r="R16" t="n">
-        <v>7331217</v>
+        <v>7331205</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135350593</v>
+        <v>135350590</v>
       </c>
       <c r="B17" t="n">
-        <v>80493</v>
+        <v>92320</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>2063</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600068</v>
+        <v>600137</v>
       </c>
       <c r="R17" t="n">
-        <v>7331214</v>
+        <v>7331217</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2276,6 +2276,117 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,48 +1950,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135351898</v>
+        <v>135354303</v>
       </c>
       <c r="B15" t="n">
-        <v>79452</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600023</v>
+        <v>599499</v>
       </c>
       <c r="R15" t="n">
-        <v>7331182</v>
+        <v>7330997</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2045,12 +2045,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135350592</v>
+        <v>135351898</v>
       </c>
       <c r="B16" t="n">
         <v>79452</v>
@@ -2092,17 +2092,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600105</v>
+        <v>600023</v>
       </c>
       <c r="R16" t="n">
-        <v>7331205</v>
+        <v>7331182</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2156,12 +2156,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135350590</v>
+        <v>135350592</v>
       </c>
       <c r="B17" t="n">
-        <v>92320</v>
+        <v>79452</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2063</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600137</v>
+        <v>600105</v>
       </c>
       <c r="R17" t="n">
-        <v>7331217</v>
+        <v>7331205</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2283,32 +2283,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135350593</v>
+        <v>135350590</v>
       </c>
       <c r="B18" t="n">
-        <v>80493</v>
+        <v>92320</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2063</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600068</v>
+        <v>600137</v>
       </c>
       <c r="R18" t="n">
-        <v>7331214</v>
+        <v>7331217</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2387,6 +2387,117 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91798</v>
+        <v>135356212</v>
       </c>
       <c r="B2" t="n">
-        <v>78350</v>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599140</v>
+        <v>598630</v>
       </c>
       <c r="R2" t="n">
-        <v>7330614</v>
+        <v>7330419</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,60 +770,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>215318</v>
+        <v>135356208</v>
       </c>
       <c r="B3" t="n">
-        <v>92208</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>2063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599140</v>
+        <v>598597</v>
       </c>
       <c r="R3" t="n">
-        <v>7330614</v>
+        <v>7330356</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,60 +881,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>302676</v>
+        <v>135356210</v>
       </c>
       <c r="B4" t="n">
-        <v>91905</v>
+        <v>92370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599140</v>
+        <v>598603</v>
       </c>
       <c r="R4" t="n">
-        <v>7330614</v>
+        <v>7330411</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,60 +992,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>405628</v>
+        <v>135356209</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>106309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599140</v>
+        <v>598597</v>
       </c>
       <c r="R5" t="n">
-        <v>7330614</v>
+        <v>7330383</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1073,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,57 +1103,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135350748</v>
+        <v>135356206</v>
       </c>
       <c r="B6" t="n">
-        <v>91974</v>
+        <v>98060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599345</v>
+        <v>598569</v>
       </c>
       <c r="R6" t="n">
-        <v>7330968</v>
+        <v>7330354</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1133,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1143,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1158,12 +1214,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1174,48 +1230,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>334447</v>
+        <v>135356211</v>
       </c>
       <c r="B7" t="n">
-        <v>91923</v>
+        <v>99217</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599140</v>
+        <v>598644</v>
       </c>
       <c r="R7" t="n">
-        <v>7330614</v>
+        <v>7330364</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1239,12 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1259,60 +1325,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>376098</v>
+        <v>135356213</v>
       </c>
       <c r="B8" t="n">
-        <v>92369</v>
+        <v>99217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599140</v>
+        <v>598651</v>
       </c>
       <c r="R8" t="n">
-        <v>7330614</v>
+        <v>7330373</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1336,12 +1406,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1356,22 +1436,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>385987</v>
+        <v>135356215</v>
       </c>
       <c r="B9" t="n">
-        <v>83173</v>
+        <v>91970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,37 +1463,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599140</v>
+        <v>598722</v>
       </c>
       <c r="R9" t="n">
-        <v>7330614</v>
+        <v>7330312</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1433,12 +1517,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1453,60 +1547,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>520073</v>
+        <v>135356216</v>
       </c>
       <c r="B10" t="n">
-        <v>92292</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599140</v>
+        <v>598747</v>
       </c>
       <c r="R10" t="n">
-        <v>7330614</v>
+        <v>7330309</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1530,12 +1628,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1550,60 +1663,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>414990</v>
+        <v>135356218</v>
       </c>
       <c r="B11" t="n">
-        <v>92097</v>
+        <v>106309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1588</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599140</v>
+        <v>598785</v>
       </c>
       <c r="R11" t="n">
-        <v>7330614</v>
+        <v>7330366</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1627,12 +1744,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1647,44 +1774,48 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1120620</v>
+        <v>91798</v>
       </c>
       <c r="B12" t="n">
-        <v>92632</v>
+        <v>78350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,39 +1880,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1886847</v>
+        <v>215318</v>
       </c>
       <c r="B13" t="n">
-        <v>92333</v>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,32 +1984,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4043291</v>
+        <v>302676</v>
       </c>
       <c r="B14" t="n">
-        <v>106229</v>
+        <v>91905</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,48 +2081,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135354303</v>
+        <v>405628</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599499</v>
+        <v>599140</v>
       </c>
       <c r="R15" t="n">
-        <v>7330997</v>
+        <v>7330614</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2015,22 +2146,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2045,26 +2166,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135351898</v>
+        <v>135350748</v>
       </c>
       <c r="B16" t="n">
-        <v>79452</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,37 +2189,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600023</v>
+        <v>599345</v>
       </c>
       <c r="R16" t="n">
-        <v>7331182</v>
+        <v>7330968</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2141,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2156,12 +2273,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2172,48 +2289,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135350592</v>
+        <v>334447</v>
       </c>
       <c r="B17" t="n">
-        <v>79452</v>
+        <v>91923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600105</v>
+        <v>599140</v>
       </c>
       <c r="R17" t="n">
-        <v>7331205</v>
+        <v>7330614</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2237,22 +2354,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2267,64 +2374,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135350590</v>
+        <v>376098</v>
       </c>
       <c r="B18" t="n">
-        <v>92320</v>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2063</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600137</v>
+        <v>599140</v>
       </c>
       <c r="R18" t="n">
-        <v>7331217</v>
+        <v>7330614</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2348,22 +2451,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2378,64 +2471,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135350593</v>
+        <v>385987</v>
       </c>
       <c r="B19" t="n">
-        <v>80493</v>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600068</v>
+        <v>599140</v>
       </c>
       <c r="R19" t="n">
-        <v>7331214</v>
+        <v>7330614</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2459,22 +2548,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2489,15 +2568,1384 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>520073</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>414990</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92097</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1120620</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S22" t="n">
+        <v>100</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1886847</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92333</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4043291</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S24" t="n">
+        <v>100</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135354303</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>599499</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7330997</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135351898</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>864</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600023</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7331182</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135350679</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78393</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>314</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600102</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7331208</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135350592</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>864</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600105</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7331205</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135350677</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>864</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7331204</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135350680</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83363</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7331204</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135350590</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92320</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>600137</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7331217</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135356215</v>
+        <v>135356244</v>
       </c>
       <c r="B9" t="n">
-        <v>91970</v>
+        <v>92245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,13 +1487,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598722</v>
+        <v>598482</v>
       </c>
       <c r="R9" t="n">
-        <v>7330312</v>
+        <v>7330539</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135356216</v>
+        <v>135356242</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598747</v>
+        <v>598483</v>
       </c>
       <c r="R10" t="n">
-        <v>7330309</v>
+        <v>7330545</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,12 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135356218</v>
+        <v>135356239</v>
       </c>
       <c r="B11" t="n">
-        <v>106309</v>
+        <v>92320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598785</v>
+        <v>598515</v>
       </c>
       <c r="R11" t="n">
-        <v>7330366</v>
+        <v>7330567</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>91798</v>
+        <v>135356240</v>
       </c>
       <c r="B12" t="n">
-        <v>78350</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,37 +1796,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599140</v>
+        <v>598519</v>
       </c>
       <c r="R12" t="n">
-        <v>7330614</v>
+        <v>7330561</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,12 +1850,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,60 +1880,64 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>215318</v>
+        <v>135356241</v>
       </c>
       <c r="B13" t="n">
-        <v>92208</v>
+        <v>109924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>221184</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599140</v>
+        <v>598490</v>
       </c>
       <c r="R13" t="n">
-        <v>7330614</v>
+        <v>7330565</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,12 +1961,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,60 +1991,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>302676</v>
+        <v>135356243</v>
       </c>
       <c r="B14" t="n">
-        <v>91905</v>
+        <v>98060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599140</v>
+        <v>598482</v>
       </c>
       <c r="R14" t="n">
-        <v>7330614</v>
+        <v>7330539</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,12 +2072,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,22 +2102,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>405628</v>
+        <v>135356215</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>91970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,37 +2129,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599140</v>
+        <v>598722</v>
       </c>
       <c r="R15" t="n">
-        <v>7330614</v>
+        <v>7330312</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,12 +2183,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,22 +2213,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135350748</v>
+        <v>135356221</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,37 +2240,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599345</v>
+        <v>598915</v>
       </c>
       <c r="R16" t="n">
-        <v>7330968</v>
+        <v>7330353</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2299,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2309,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,12 +2324,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2289,48 +2340,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>334447</v>
+        <v>135356220</v>
       </c>
       <c r="B17" t="n">
-        <v>91923</v>
+        <v>91974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599140</v>
+        <v>598838</v>
       </c>
       <c r="R17" t="n">
-        <v>7330614</v>
+        <v>7330376</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2354,12 +2405,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2374,22 +2435,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>376098</v>
+        <v>135356223</v>
       </c>
       <c r="B18" t="n">
-        <v>92369</v>
+        <v>83222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,37 +2462,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599140</v>
+        <v>599215</v>
       </c>
       <c r="R18" t="n">
-        <v>7330614</v>
+        <v>7330319</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2451,12 +2516,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2471,22 +2546,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>385987</v>
+        <v>135356224</v>
       </c>
       <c r="B19" t="n">
-        <v>83173</v>
+        <v>83222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,17 +2593,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599140</v>
+        <v>599218</v>
       </c>
       <c r="R19" t="n">
-        <v>7330614</v>
+        <v>7330320</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2548,12 +2627,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2568,60 +2657,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>520073</v>
+        <v>135356222</v>
       </c>
       <c r="B20" t="n">
-        <v>92292</v>
+        <v>83358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1506</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599140</v>
+        <v>599167</v>
       </c>
       <c r="R20" t="n">
-        <v>7330614</v>
+        <v>7330330</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2645,12 +2738,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2665,22 +2768,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>414990</v>
+        <v>135356216</v>
       </c>
       <c r="B21" t="n">
-        <v>92097</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,37 +2795,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599140</v>
+        <v>598747</v>
       </c>
       <c r="R21" t="n">
-        <v>7330614</v>
+        <v>7330309</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2742,12 +2849,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2762,22 +2884,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1120620</v>
+        <v>135356218</v>
       </c>
       <c r="B22" t="n">
-        <v>92632</v>
+        <v>106309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,37 +2911,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599140</v>
+        <v>598785</v>
       </c>
       <c r="R22" t="n">
-        <v>7330614</v>
+        <v>7330366</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2839,12 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2859,44 +2995,48 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1886847</v>
+        <v>91798</v>
       </c>
       <c r="B23" t="n">
-        <v>92333</v>
+        <v>78350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4217</v>
+        <v>314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,32 +3108,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4043291</v>
+        <v>215318</v>
       </c>
       <c r="B24" t="n">
-        <v>106229</v>
+        <v>92208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3065,48 +3205,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135354303</v>
+        <v>302676</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599499</v>
+        <v>599140</v>
       </c>
       <c r="R25" t="n">
-        <v>7330997</v>
+        <v>7330614</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3130,22 +3270,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3160,26 +3290,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135351898</v>
+        <v>405628</v>
       </c>
       <c r="B26" t="n">
-        <v>79452</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,37 +3313,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600023</v>
+        <v>599140</v>
       </c>
       <c r="R26" t="n">
-        <v>7331182</v>
+        <v>7330614</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3241,22 +3367,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3271,61 +3387,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135350679</v>
+        <v>135350748</v>
       </c>
       <c r="B27" t="n">
-        <v>78393</v>
+        <v>91974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600102</v>
+        <v>599345</v>
       </c>
       <c r="R27" t="n">
-        <v>7331208</v>
+        <v>7330968</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3357,7 +3469,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3367,7 +3479,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,12 +3494,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3398,48 +3510,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135350592</v>
+        <v>334447</v>
       </c>
       <c r="B28" t="n">
-        <v>79452</v>
+        <v>91923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600105</v>
+        <v>599140</v>
       </c>
       <c r="R28" t="n">
-        <v>7331205</v>
+        <v>7330614</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3463,22 +3575,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:49</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3493,26 +3595,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135350677</v>
+        <v>376098</v>
       </c>
       <c r="B29" t="n">
-        <v>79452</v>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3520,37 +3618,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600100</v>
+        <v>599140</v>
       </c>
       <c r="R29" t="n">
-        <v>7331204</v>
+        <v>7330614</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3574,22 +3672,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3604,26 +3692,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135350680</v>
+        <v>385987</v>
       </c>
       <c r="B30" t="n">
-        <v>83363</v>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3631,37 +3715,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600100</v>
+        <v>599140</v>
       </c>
       <c r="R30" t="n">
-        <v>7331204</v>
+        <v>7330614</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3685,22 +3769,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,26 +3789,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135350590</v>
+        <v>520073</v>
       </c>
       <c r="B31" t="n">
-        <v>92320</v>
+        <v>92292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3742,37 +3812,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2063</v>
+        <v>1506</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>600137</v>
+        <v>599140</v>
       </c>
       <c r="R31" t="n">
-        <v>7331217</v>
+        <v>7330614</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3796,22 +3866,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3826,64 +3886,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135350593</v>
+        <v>414990</v>
       </c>
       <c r="B32" t="n">
-        <v>80493</v>
+        <v>92097</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>600068</v>
+        <v>599140</v>
       </c>
       <c r="R32" t="n">
-        <v>7331214</v>
+        <v>7330614</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3907,22 +3963,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,15 +3983,2083 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1120620</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1886847</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92333</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S34" t="n">
+        <v>100</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135356234</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>598751</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7330559</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135356235</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>598695</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7330539</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4043291</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>599140</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7330614</v>
+      </c>
+      <c r="S37" t="n">
+        <v>100</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2003-10-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135356231</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>599605</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7330435</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135356227</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>599545</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7330200</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135356228</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92370</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>599545</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7330200</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135356230</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>599798</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7330302</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135356226</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>599438</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7330252</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135356229</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>599557</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7330190</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135354303</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>599499</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7330997</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135351898</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>864</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>600023</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7331182</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135350679</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78393</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>314</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>600102</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7331208</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135350592</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>864</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>600105</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7331205</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135350677</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>864</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7331204</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135350680</v>
+      </c>
+      <c r="B49" t="n">
+        <v>83363</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7331204</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135350590</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92320</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>600137</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7331217</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S51" t="n">
+        <v>7</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135356212</v>
+        <v>135356377</v>
       </c>
       <c r="B2" t="n">
-        <v>92329</v>
+        <v>90996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>58</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Isabellporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Anomoporia bombycina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598630</v>
+        <v>598665</v>
       </c>
       <c r="R2" t="n">
-        <v>7330419</v>
+        <v>7330380</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,27 +755,28 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135356208</v>
+        <v>135356375</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2063</v>
+        <v>318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Bågknotterskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Kneiffiella curvispora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(J.Erikss. &amp; Hjortstam) Jülich &amp; Stalpers</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598597</v>
+        <v>598599</v>
       </c>
       <c r="R3" t="n">
-        <v>7330356</v>
+        <v>7330369</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,27 +867,28 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,48 +899,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135356210</v>
+        <v>135356374</v>
       </c>
       <c r="B4" t="n">
-        <v>92370</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598603</v>
+        <v>598548</v>
       </c>
       <c r="R4" t="n">
-        <v>7330411</v>
+        <v>7330375</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,32 +1010,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135356209</v>
+        <v>135356212</v>
       </c>
       <c r="B5" t="n">
-        <v>106309</v>
+        <v>92329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,13 +1045,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598597</v>
+        <v>598630</v>
       </c>
       <c r="R5" t="n">
-        <v>7330383</v>
+        <v>7330419</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,32 +1121,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135356206</v>
+        <v>135356208</v>
       </c>
       <c r="B6" t="n">
-        <v>98060</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598569</v>
+        <v>598597</v>
       </c>
       <c r="R6" t="n">
-        <v>7330354</v>
+        <v>7330356</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135356211</v>
+        <v>135356210</v>
       </c>
       <c r="B7" t="n">
-        <v>99217</v>
+        <v>92370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598644</v>
+        <v>598603</v>
       </c>
       <c r="R7" t="n">
-        <v>7330364</v>
+        <v>7330411</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135356213</v>
+        <v>135356372</v>
       </c>
       <c r="B8" t="n">
-        <v>99217</v>
+        <v>92370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,37 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598651</v>
+        <v>598544</v>
       </c>
       <c r="R8" t="n">
-        <v>7330373</v>
+        <v>7330366</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,12 +1438,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1452,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135356244</v>
+        <v>135356376</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,34 +1465,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598482</v>
+        <v>598614</v>
       </c>
       <c r="R9" t="n">
-        <v>7330539</v>
+        <v>7330356</v>
       </c>
       <c r="S9" t="n">
         <v>7</v>
@@ -1522,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1532,14 +1542,19 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1547,12 +1562,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1563,32 +1578,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135356242</v>
+        <v>135356209</v>
       </c>
       <c r="B10" t="n">
-        <v>91970</v>
+        <v>106309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598483</v>
+        <v>598597</v>
       </c>
       <c r="R10" t="n">
-        <v>7330545</v>
+        <v>7330383</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1648,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1658,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,32 +1689,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135356239</v>
+        <v>135356206</v>
       </c>
       <c r="B11" t="n">
-        <v>92320</v>
+        <v>98060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598515</v>
+        <v>598569</v>
       </c>
       <c r="R11" t="n">
-        <v>7330567</v>
+        <v>7330354</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1744,7 +1759,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1769,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,32 +1800,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135356240</v>
+        <v>135356211</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>99217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598519</v>
+        <v>598644</v>
       </c>
       <c r="R12" t="n">
-        <v>7330561</v>
+        <v>7330364</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1855,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135356241</v>
+        <v>135356213</v>
       </c>
       <c r="B13" t="n">
-        <v>109924</v>
+        <v>99217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1922,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221184</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,13 +1946,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598490</v>
+        <v>598651</v>
       </c>
       <c r="R13" t="n">
-        <v>7330565</v>
+        <v>7330373</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1981,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1991,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,32 +2022,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135356243</v>
+        <v>135356244</v>
       </c>
       <c r="B14" t="n">
-        <v>98060</v>
+        <v>92245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2048,7 +2063,7 @@
         <v>7330539</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2092,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2102,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135356215</v>
+        <v>135356242</v>
       </c>
       <c r="B15" t="n">
         <v>91970</v>
@@ -2153,13 +2168,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598722</v>
+        <v>598483</v>
       </c>
       <c r="R15" t="n">
-        <v>7330312</v>
+        <v>7330545</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,7 +2203,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,7 +2213,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2229,32 +2244,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135356221</v>
+        <v>135356239</v>
       </c>
       <c r="B16" t="n">
-        <v>91970</v>
+        <v>92320</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,13 +2279,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598915</v>
+        <v>598515</v>
       </c>
       <c r="R16" t="n">
-        <v>7330353</v>
+        <v>7330567</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,7 +2314,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2309,7 +2324,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,32 +2355,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135356220</v>
+        <v>135356240</v>
       </c>
       <c r="B17" t="n">
-        <v>91974</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,13 +2390,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598838</v>
+        <v>598519</v>
       </c>
       <c r="R17" t="n">
-        <v>7330376</v>
+        <v>7330561</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2425,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2435,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2451,32 +2466,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135356223</v>
+        <v>135356241</v>
       </c>
       <c r="B18" t="n">
-        <v>83222</v>
+        <v>109924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>221184</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599215</v>
+        <v>598490</v>
       </c>
       <c r="R18" t="n">
-        <v>7330319</v>
+        <v>7330565</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2521,7 +2536,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2531,7 +2546,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,32 +2577,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135356224</v>
+        <v>135356243</v>
       </c>
       <c r="B19" t="n">
-        <v>83222</v>
+        <v>98060</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2597,13 +2612,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599218</v>
+        <v>598482</v>
       </c>
       <c r="R19" t="n">
-        <v>7330320</v>
+        <v>7330539</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2647,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2657,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,10 +2688,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135356222</v>
+        <v>135356379</v>
       </c>
       <c r="B20" t="n">
-        <v>83358</v>
+        <v>92245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2684,37 +2699,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599167</v>
+        <v>598877</v>
       </c>
       <c r="R20" t="n">
-        <v>7330330</v>
+        <v>7330349</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,7 +2758,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2753,7 +2768,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2768,12 +2783,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2784,10 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135356216</v>
+        <v>135356215</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>91970</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2795,21 +2810,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2819,10 +2834,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598747</v>
+        <v>598722</v>
       </c>
       <c r="R21" t="n">
-        <v>7330309</v>
+        <v>7330312</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -2854,7 +2869,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2864,12 +2879,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gamla och nya ringhack</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,32 +2910,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135356218</v>
+        <v>135356221</v>
       </c>
       <c r="B22" t="n">
-        <v>106309</v>
+        <v>91970</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2935,13 +2945,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>598785</v>
+        <v>598915</v>
       </c>
       <c r="R22" t="n">
-        <v>7330366</v>
+        <v>7330353</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2970,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2990,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3011,48 +3021,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>91798</v>
+        <v>135356220</v>
       </c>
       <c r="B23" t="n">
-        <v>78350</v>
+        <v>91974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599140</v>
+        <v>598838</v>
       </c>
       <c r="R23" t="n">
-        <v>7330614</v>
+        <v>7330376</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3076,12 +3086,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,60 +3116,67 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>215318</v>
+        <v>135356378</v>
       </c>
       <c r="B24" t="n">
-        <v>92208</v>
+        <v>91988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599140</v>
+        <v>598724</v>
       </c>
       <c r="R24" t="n">
-        <v>7330614</v>
+        <v>7330323</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,12 +3200,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3187,28 +3224,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>302676</v>
+        <v>135356223</v>
       </c>
       <c r="B25" t="n">
-        <v>91905</v>
+        <v>83222</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,37 +3258,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599140</v>
+        <v>599215</v>
       </c>
       <c r="R25" t="n">
-        <v>7330614</v>
+        <v>7330319</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3270,12 +3312,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,22 +3342,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>405628</v>
+        <v>135356224</v>
       </c>
       <c r="B26" t="n">
-        <v>91909</v>
+        <v>83222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,37 +3369,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599140</v>
+        <v>599218</v>
       </c>
       <c r="R26" t="n">
-        <v>7330614</v>
+        <v>7330320</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3367,12 +3423,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3387,22 +3453,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135350748</v>
+        <v>135356222</v>
       </c>
       <c r="B27" t="n">
-        <v>91974</v>
+        <v>83358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3410,34 +3480,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599345</v>
+        <v>599167</v>
       </c>
       <c r="R27" t="n">
-        <v>7330968</v>
+        <v>7330330</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3469,7 +3539,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3479,7 +3549,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3494,12 +3564,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3510,48 +3580,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>334447</v>
+        <v>135356216</v>
       </c>
       <c r="B28" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599140</v>
+        <v>598747</v>
       </c>
       <c r="R28" t="n">
-        <v>7330614</v>
+        <v>7330309</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3575,12 +3645,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gamla och nya ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3595,22 +3680,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>376098</v>
+        <v>135356380</v>
       </c>
       <c r="B29" t="n">
-        <v>92369</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,37 +3707,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599140</v>
+        <v>598877</v>
       </c>
       <c r="R29" t="n">
-        <v>7330614</v>
+        <v>7330349</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3672,12 +3769,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3692,60 +3804,64 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>385987</v>
+        <v>135356218</v>
       </c>
       <c r="B30" t="n">
-        <v>83173</v>
+        <v>106309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>221725</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599140</v>
+        <v>598785</v>
       </c>
       <c r="R30" t="n">
-        <v>7330614</v>
+        <v>7330366</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3769,12 +3885,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3789,22 +3915,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Linda Johansson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>520073</v>
+        <v>91798</v>
       </c>
       <c r="B31" t="n">
-        <v>92292</v>
+        <v>78350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3812,21 +3942,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1506</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3898,10 +4028,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>414990</v>
+        <v>215318</v>
       </c>
       <c r="B32" t="n">
-        <v>92097</v>
+        <v>92208</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3909,21 +4039,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3988,39 +4118,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1120620</v>
+        <v>302676</v>
       </c>
       <c r="B33" t="n">
-        <v>92632</v>
+        <v>91905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4085,39 +4215,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Via Linda Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1886847</v>
+        <v>405628</v>
       </c>
       <c r="B34" t="n">
-        <v>92333</v>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4189,45 +4319,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135356234</v>
+        <v>135350748</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>598751</v>
+        <v>599345</v>
       </c>
       <c r="R35" t="n">
-        <v>7330559</v>
+        <v>7330968</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4259,7 +4389,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4269,7 +4399,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4284,12 +4414,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4300,48 +4430,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135356235</v>
+        <v>334447</v>
       </c>
       <c r="B36" t="n">
-        <v>58136</v>
+        <v>91923</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>598695</v>
+        <v>599140</v>
       </c>
       <c r="R36" t="n">
-        <v>7330539</v>
+        <v>7330614</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4365,22 +4495,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,48 +4515,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4043291</v>
+        <v>376098</v>
       </c>
       <c r="B37" t="n">
-        <v>106229</v>
+        <v>92369</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221725</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4508,10 +4624,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135356231</v>
+        <v>385987</v>
       </c>
       <c r="B38" t="n">
-        <v>91970</v>
+        <v>83173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,37 +4635,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599605</v>
+        <v>599140</v>
       </c>
       <c r="R38" t="n">
-        <v>7330435</v>
+        <v>7330614</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4573,22 +4689,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,26 +4709,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135356227</v>
+        <v>520073</v>
       </c>
       <c r="B39" t="n">
-        <v>92329</v>
+        <v>92292</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,17 +4752,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599545</v>
+        <v>599140</v>
       </c>
       <c r="R39" t="n">
-        <v>7330200</v>
+        <v>7330614</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4684,22 +4786,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4714,64 +4806,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135356228</v>
+        <v>414990</v>
       </c>
       <c r="B40" t="n">
-        <v>92370</v>
+        <v>92097</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4217</v>
+        <v>1588</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599545</v>
+        <v>599140</v>
       </c>
       <c r="R40" t="n">
-        <v>7330200</v>
+        <v>7330614</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4795,22 +4883,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4825,64 +4903,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135356230</v>
+        <v>1120620</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>92632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599798</v>
+        <v>599140</v>
       </c>
       <c r="R41" t="n">
-        <v>7330302</v>
+        <v>7330614</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4906,27 +4980,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4941,26 +5000,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135356226</v>
+        <v>1886847</v>
       </c>
       <c r="B42" t="n">
-        <v>99217</v>
+        <v>92333</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4968,37 +5023,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>4217</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599438</v>
+        <v>599140</v>
       </c>
       <c r="R42" t="n">
-        <v>7330252</v>
+        <v>7330614</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5022,22 +5077,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:13</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5052,48 +5097,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135356229</v>
+        <v>135356234</v>
       </c>
       <c r="B43" t="n">
-        <v>99217</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5103,10 +5144,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599557</v>
+        <v>598751</v>
       </c>
       <c r="R43" t="n">
-        <v>7330190</v>
+        <v>7330559</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5138,7 +5179,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5148,7 +5189,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5179,7 +5220,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135354303</v>
+        <v>135356383</v>
       </c>
       <c r="B44" t="n">
         <v>79373</v>
@@ -5210,17 +5251,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599499</v>
+        <v>599257</v>
       </c>
       <c r="R44" t="n">
-        <v>7330997</v>
+        <v>7330821</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5249,7 +5290,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5259,7 +5300,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,12 +5315,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5290,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135351898</v>
+        <v>135356382</v>
       </c>
       <c r="B45" t="n">
-        <v>79452</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,37 +5342,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>600023</v>
+        <v>599266</v>
       </c>
       <c r="R45" t="n">
-        <v>7331182</v>
+        <v>7330819</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5360,7 +5409,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5370,7 +5419,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5385,12 +5439,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5401,45 +5455,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135350679</v>
+        <v>135356235</v>
       </c>
       <c r="B46" t="n">
-        <v>78393</v>
+        <v>58136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>314</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>600102</v>
+        <v>598695</v>
       </c>
       <c r="R46" t="n">
-        <v>7331208</v>
+        <v>7330539</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5471,7 +5525,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5535,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5496,12 +5550,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5512,48 +5566,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135350592</v>
+        <v>135356384</v>
       </c>
       <c r="B47" t="n">
-        <v>79452</v>
+        <v>99112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>600105</v>
+        <v>599003</v>
       </c>
       <c r="R47" t="n">
-        <v>7331205</v>
+        <v>7330499</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5582,7 +5636,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5592,7 +5646,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5607,12 +5661,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5623,48 +5677,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135350677</v>
+        <v>4043291</v>
       </c>
       <c r="B48" t="n">
-        <v>79452</v>
+        <v>106229</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive 5,5 km S om Laisvall, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>600100</v>
+        <v>599140</v>
       </c>
       <c r="R48" t="n">
-        <v>7331204</v>
+        <v>7330614</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5688,22 +5742,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,26 +5762,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Linda Johansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Via Linda Johansson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135350680</v>
+        <v>135356231</v>
       </c>
       <c r="B49" t="n">
-        <v>83363</v>
+        <v>91970</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5745,34 +5785,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>600100</v>
+        <v>599605</v>
       </c>
       <c r="R49" t="n">
-        <v>7331204</v>
+        <v>7330435</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5804,7 +5844,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5814,7 +5854,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5829,12 +5869,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5845,10 +5885,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135350590</v>
+        <v>135356227</v>
       </c>
       <c r="B50" t="n">
-        <v>92320</v>
+        <v>92329</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5856,37 +5896,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2063</v>
+        <v>1506</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>600137</v>
+        <v>599545</v>
       </c>
       <c r="R50" t="n">
-        <v>7331217</v>
+        <v>7330200</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5915,7 +5955,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5925,7 +5965,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5940,12 +5980,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5956,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135350593</v>
+        <v>135356228</v>
       </c>
       <c r="B51" t="n">
-        <v>80493</v>
+        <v>92370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,37 +6007,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>4217</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>600068</v>
+        <v>599545</v>
       </c>
       <c r="R51" t="n">
-        <v>7331214</v>
+        <v>7330200</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6026,7 +6066,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6036,7 +6076,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6051,15 +6091,1365 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135356230</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>599798</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7330302</v>
+      </c>
+      <c r="S52" t="n">
+        <v>8</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Spår</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135356226</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>599438</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7330252</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135356229</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>599557</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7330190</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135354303</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>599499</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7330997</v>
+      </c>
+      <c r="S55" t="n">
+        <v>6</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135356381</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>599631</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7330482</v>
+      </c>
+      <c r="S56" t="n">
+        <v>9</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135351898</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>864</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>600023</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7331182</v>
+      </c>
+      <c r="S57" t="n">
+        <v>8</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135350679</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78393</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>314</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>600102</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7331208</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135350592</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>864</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>600105</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7331205</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135350677</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79452</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>864</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7331204</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135350680</v>
+      </c>
+      <c r="B61" t="n">
+        <v>83363</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>600100</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7331204</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135350590</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92320</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>600137</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7331217</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S63" t="n">
+        <v>7</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY338"/>
+  <dimension ref="A1:AY339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28513,10 +28513,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>135357178</v>
+        <v>135383915</v>
       </c>
       <c r="B253" t="n">
-        <v>102871</v>
+        <v>99205</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28524,34 +28524,34 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>223037</v>
+        <v>222495</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Myggblomster</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Hammarbya paludosa</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Kuntze</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive N, Pi lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>598885</v>
+        <v>598692</v>
       </c>
       <c r="R253" t="n">
-        <v>7330511</v>
+        <v>7330748</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28578,22 +28578,22 @@
       </c>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28608,12 +28608,12 @@
       <c r="AT253" t="inlineStr"/>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -28624,10 +28624,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>135357190</v>
+        <v>135357178</v>
       </c>
       <c r="B254" t="n">
-        <v>98249</v>
+        <v>102871</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28635,21 +28635,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>223358</v>
+        <v>223037</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -28659,10 +28659,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>598714</v>
+        <v>598885</v>
       </c>
       <c r="R254" t="n">
-        <v>7330606</v>
+        <v>7330511</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28704,7 +28704,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD254" t="b">
@@ -28735,10 +28735,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>135357169</v>
+        <v>135357190</v>
       </c>
       <c r="B255" t="n">
-        <v>101293</v>
+        <v>98249</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28746,21 +28746,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>224885</v>
+        <v>223358</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -28770,10 +28770,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>599122</v>
+        <v>598714</v>
       </c>
       <c r="R255" t="n">
-        <v>7330671</v>
+        <v>7330606</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD255" t="b">
@@ -28846,7 +28846,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>135357177</v>
+        <v>135357169</v>
       </c>
       <c r="B256" t="n">
         <v>101293</v>
@@ -28881,10 +28881,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>598885</v>
+        <v>599122</v>
       </c>
       <c r="R256" t="n">
-        <v>7330511</v>
+        <v>7330671</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -28916,7 +28916,7 @@
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD256" t="b">
@@ -28957,7 +28957,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>135357182</v>
+        <v>135357177</v>
       </c>
       <c r="B257" t="n">
         <v>101293</v>
@@ -28992,10 +28992,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>598835</v>
+        <v>598885</v>
       </c>
       <c r="R257" t="n">
-        <v>7330568</v>
+        <v>7330511</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD257" t="b">
@@ -29068,7 +29068,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>135357183</v>
+        <v>135357182</v>
       </c>
       <c r="B258" t="n">
         <v>101293</v>
@@ -29103,10 +29103,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>598798</v>
+        <v>598835</v>
       </c>
       <c r="R258" t="n">
-        <v>7330630</v>
+        <v>7330568</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="Z258" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -29148,7 +29148,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD258" t="b">
@@ -29179,7 +29179,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>135357186</v>
+        <v>135357183</v>
       </c>
       <c r="B259" t="n">
         <v>101293</v>
@@ -29214,10 +29214,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>598792</v>
+        <v>598798</v>
       </c>
       <c r="R259" t="n">
-        <v>7330626</v>
+        <v>7330630</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -29290,7 +29290,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>135357188</v>
+        <v>135357186</v>
       </c>
       <c r="B260" t="n">
         <v>101293</v>
@@ -29325,10 +29325,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>598718</v>
+        <v>598792</v>
       </c>
       <c r="R260" t="n">
-        <v>7330629</v>
+        <v>7330626</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -29360,7 +29360,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -29370,7 +29370,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29401,7 +29401,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>135357191</v>
+        <v>135357188</v>
       </c>
       <c r="B261" t="n">
         <v>101293</v>
@@ -29436,10 +29436,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>598692</v>
+        <v>598718</v>
       </c>
       <c r="R261" t="n">
-        <v>7330626</v>
+        <v>7330629</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29471,7 +29471,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29512,48 +29512,48 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>135353538</v>
+        <v>135357191</v>
       </c>
       <c r="B262" t="n">
-        <v>78393</v>
+        <v>101293</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>314</v>
+        <v>224885</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>599385</v>
+        <v>598692</v>
       </c>
       <c r="R262" t="n">
-        <v>7330278</v>
+        <v>7330626</v>
       </c>
       <c r="S262" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -29592,7 +29592,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29601,19 +29601,18 @@
       <c r="AE262" t="b">
         <v>0</v>
       </c>
-      <c r="AF262" t="inlineStr"/>
       <c r="AG262" t="b">
         <v>0</v>
       </c>
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
@@ -29624,45 +29623,45 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>135356867</v>
+        <v>135353538</v>
       </c>
       <c r="B263" t="n">
-        <v>92245</v>
+        <v>78393</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>658</v>
+        <v>314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>599566</v>
+        <v>599385</v>
       </c>
       <c r="R263" t="n">
-        <v>7330173</v>
+        <v>7330278</v>
       </c>
       <c r="S263" t="n">
         <v>5</v>
@@ -29694,7 +29693,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -29704,7 +29703,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD263" t="b">
@@ -29713,18 +29712,19 @@
       <c r="AE263" t="b">
         <v>0</v>
       </c>
+      <c r="AF263" t="inlineStr"/>
       <c r="AG263" t="b">
         <v>0</v>
       </c>
       <c r="AT263" t="inlineStr"/>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
@@ -29735,10 +29735,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>135353549</v>
+        <v>135356867</v>
       </c>
       <c r="B264" t="n">
-        <v>91970</v>
+        <v>92245</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -29746,34 +29746,34 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>599732</v>
+        <v>599566</v>
       </c>
       <c r="R264" t="n">
-        <v>7330270</v>
+        <v>7330173</v>
       </c>
       <c r="S264" t="n">
         <v>5</v>
@@ -29805,7 +29805,7 @@
       </c>
       <c r="Z264" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -29815,7 +29815,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -29830,12 +29830,12 @@
       <c r="AT264" t="inlineStr"/>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
@@ -29846,7 +29846,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>135356231</v>
+        <v>135353549</v>
       </c>
       <c r="B265" t="n">
         <v>91970</v>
@@ -29877,14 +29877,14 @@
       <c r="I265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>599605</v>
+        <v>599732</v>
       </c>
       <c r="R265" t="n">
-        <v>7330435</v>
+        <v>7330270</v>
       </c>
       <c r="S265" t="n">
         <v>5</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="Z265" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA265" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD265" t="b">
@@ -29941,12 +29941,12 @@
       <c r="AT265" t="inlineStr"/>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
@@ -29957,7 +29957,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>135356870</v>
+        <v>135356231</v>
       </c>
       <c r="B266" t="n">
         <v>91970</v>
@@ -29988,17 +29988,17 @@
       <c r="I266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>599684</v>
+        <v>599605</v>
       </c>
       <c r="R266" t="n">
-        <v>7330432</v>
+        <v>7330435</v>
       </c>
       <c r="S266" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="Z266" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD266" t="b">
@@ -30052,12 +30052,12 @@
       <c r="AT266" t="inlineStr"/>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
@@ -30068,48 +30068,48 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>135353541</v>
+        <v>135356870</v>
       </c>
       <c r="B267" t="n">
-        <v>91988</v>
+        <v>91970</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>599375</v>
+        <v>599684</v>
       </c>
       <c r="R267" t="n">
-        <v>7330265</v>
+        <v>7330432</v>
       </c>
       <c r="S267" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -30148,7 +30148,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD267" t="b">
@@ -30163,12 +30163,12 @@
       <c r="AT267" t="inlineStr"/>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
@@ -30179,10 +30179,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>135356227</v>
+        <v>135353541</v>
       </c>
       <c r="B268" t="n">
-        <v>92329</v>
+        <v>91988</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -30190,34 +30190,34 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>1506</v>
+        <v>1204</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>599545</v>
+        <v>599375</v>
       </c>
       <c r="R268" t="n">
-        <v>7330200</v>
+        <v>7330265</v>
       </c>
       <c r="S268" t="n">
         <v>5</v>
@@ -30249,7 +30249,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -30259,7 +30259,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -30274,12 +30274,12 @@
       <c r="AT268" t="inlineStr"/>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
@@ -30290,32 +30290,32 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>135356228</v>
+        <v>135356227</v>
       </c>
       <c r="B269" t="n">
-        <v>92370</v>
+        <v>92329</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -30360,7 +30360,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -30370,7 +30370,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -30401,45 +30401,45 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>135353539</v>
+        <v>135356228</v>
       </c>
       <c r="B270" t="n">
-        <v>79373</v>
+        <v>92370</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>599380</v>
+        <v>599545</v>
       </c>
       <c r="R270" t="n">
-        <v>7330272</v>
+        <v>7330200</v>
       </c>
       <c r="S270" t="n">
         <v>5</v>
@@ -30471,7 +30471,7 @@
       </c>
       <c r="Z270" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -30481,7 +30481,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD270" t="b">
@@ -30496,12 +30496,12 @@
       <c r="AT270" t="inlineStr"/>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
@@ -30512,7 +30512,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>135353545</v>
+        <v>135353539</v>
       </c>
       <c r="B271" t="n">
         <v>79373</v>
@@ -30547,10 +30547,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>599556</v>
+        <v>599380</v>
       </c>
       <c r="R271" t="n">
-        <v>7330192</v>
+        <v>7330272</v>
       </c>
       <c r="S271" t="n">
         <v>5</v>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="Z271" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -30592,7 +30592,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD271" t="b">
@@ -30623,7 +30623,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>135356865</v>
+        <v>135353545</v>
       </c>
       <c r="B272" t="n">
         <v>79373</v>
@@ -30654,14 +30654,14 @@
       <c r="I272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>599529</v>
+        <v>599556</v>
       </c>
       <c r="R272" t="n">
-        <v>7330185</v>
+        <v>7330192</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -30693,7 +30693,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD272" t="b">
@@ -30718,12 +30718,12 @@
       <c r="AT272" t="inlineStr"/>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -30734,45 +30734,45 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>135353540</v>
+        <v>135356865</v>
       </c>
       <c r="B273" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>599380</v>
+        <v>599529</v>
       </c>
       <c r="R273" t="n">
-        <v>7330272</v>
+        <v>7330185</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -30804,7 +30804,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -30829,12 +30829,12 @@
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
@@ -30845,10 +30845,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>135356868</v>
+        <v>135353540</v>
       </c>
       <c r="B274" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -30856,34 +30856,34 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>599798</v>
+        <v>599380</v>
       </c>
       <c r="R274" t="n">
-        <v>7330244</v>
+        <v>7330272</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -30915,7 +30915,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -30925,7 +30925,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -30940,12 +30940,12 @@
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
@@ -30956,32 +30956,32 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>135356869</v>
+        <v>135356868</v>
       </c>
       <c r="B275" t="n">
-        <v>80493</v>
+        <v>80488</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -30991,10 +30991,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>599780</v>
+        <v>599798</v>
       </c>
       <c r="R275" t="n">
-        <v>7330268</v>
+        <v>7330244</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -31026,7 +31026,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -31036,7 +31036,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -31067,50 +31067,45 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>135353547</v>
+        <v>135356869</v>
       </c>
       <c r="B276" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>599585</v>
+        <v>599780</v>
       </c>
       <c r="R276" t="n">
-        <v>7330111</v>
+        <v>7330268</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -31142,7 +31137,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -31152,7 +31147,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD276" t="b">
@@ -31167,12 +31162,12 @@
       <c r="AT276" t="inlineStr"/>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
@@ -31183,7 +31178,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>135356230</v>
+        <v>135353547</v>
       </c>
       <c r="B277" t="n">
         <v>57975</v>
@@ -31212,19 +31207,24 @@
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>599798</v>
+        <v>599585</v>
       </c>
       <c r="R277" t="n">
-        <v>7330302</v>
+        <v>7330111</v>
       </c>
       <c r="S277" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -31263,12 +31263,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>Spår</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31283,12 +31278,12 @@
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
@@ -31299,48 +31294,48 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>135353543</v>
+        <v>135356230</v>
       </c>
       <c r="B278" t="n">
-        <v>98219</v>
+        <v>57975</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>219815</v>
+        <v>100109</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>599455</v>
+        <v>599798</v>
       </c>
       <c r="R278" t="n">
-        <v>7330253</v>
+        <v>7330302</v>
       </c>
       <c r="S278" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -31369,7 +31364,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -31379,7 +31374,12 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>Spår</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31394,12 +31394,12 @@
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
@@ -31410,10 +31410,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>135356871</v>
+        <v>135353543</v>
       </c>
       <c r="B279" t="n">
-        <v>106309</v>
+        <v>98219</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31421,34 +31421,34 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>599590</v>
+        <v>599455</v>
       </c>
       <c r="R279" t="n">
-        <v>7330430</v>
+        <v>7330253</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -31480,7 +31480,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -31490,7 +31490,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -31505,12 +31505,12 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
@@ -31521,10 +31521,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>135356863</v>
+        <v>135356871</v>
       </c>
       <c r="B280" t="n">
-        <v>98060</v>
+        <v>106309</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -31532,21 +31532,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -31556,10 +31556,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>599405</v>
+        <v>599590</v>
       </c>
       <c r="R280" t="n">
-        <v>7330293</v>
+        <v>7330430</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -31591,7 +31591,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD280" t="b">
@@ -31632,10 +31632,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>135353546</v>
+        <v>135356863</v>
       </c>
       <c r="B281" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31643,37 +31643,37 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>599581</v>
+        <v>599405</v>
       </c>
       <c r="R281" t="n">
-        <v>7330181</v>
+        <v>7330293</v>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -31712,7 +31712,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -31727,12 +31727,12 @@
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -31743,7 +31743,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>135353551</v>
+        <v>135353546</v>
       </c>
       <c r="B282" t="n">
         <v>99217</v>
@@ -31778,13 +31778,13 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>599839</v>
+        <v>599581</v>
       </c>
       <c r="R282" t="n">
-        <v>7330287</v>
+        <v>7330181</v>
       </c>
       <c r="S282" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -31823,7 +31823,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD282" t="b">
@@ -31854,7 +31854,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>135356226</v>
+        <v>135353551</v>
       </c>
       <c r="B283" t="n">
         <v>99217</v>
@@ -31885,14 +31885,14 @@
       <c r="I283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>599438</v>
+        <v>599839</v>
       </c>
       <c r="R283" t="n">
-        <v>7330252</v>
+        <v>7330287</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -31924,7 +31924,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD283" t="b">
@@ -31949,12 +31949,12 @@
       <c r="AT283" t="inlineStr"/>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
@@ -31965,7 +31965,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>135356229</v>
+        <v>135356226</v>
       </c>
       <c r="B284" t="n">
         <v>99217</v>
@@ -32000,10 +32000,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>599557</v>
+        <v>599438</v>
       </c>
       <c r="R284" t="n">
-        <v>7330190</v>
+        <v>7330252</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -32035,7 +32035,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -32045,7 +32045,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD284" t="b">
@@ -32076,7 +32076,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>135356864</v>
+        <v>135356229</v>
       </c>
       <c r="B285" t="n">
         <v>99217</v>
@@ -32107,14 +32107,14 @@
       <c r="I285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>599447</v>
+        <v>599557</v>
       </c>
       <c r="R285" t="n">
-        <v>7330259</v>
+        <v>7330190</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -32146,7 +32146,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -32156,7 +32156,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD285" t="b">
@@ -32171,12 +32171,12 @@
       <c r="AT285" t="inlineStr"/>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
@@ -32187,7 +32187,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>135358313</v>
+        <v>135356864</v>
       </c>
       <c r="B286" t="n">
         <v>99217</v>
@@ -32218,17 +32218,17 @@
       <c r="I286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>599395</v>
+        <v>599447</v>
       </c>
       <c r="R286" t="n">
-        <v>7330337</v>
+        <v>7330259</v>
       </c>
       <c r="S286" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -32267,7 +32267,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD286" t="b">
@@ -32282,12 +32282,12 @@
       <c r="AT286" t="inlineStr"/>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -32298,48 +32298,48 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>135353550</v>
+        <v>135358313</v>
       </c>
       <c r="B287" t="n">
-        <v>79963</v>
+        <v>99217</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>599776</v>
+        <v>599395</v>
       </c>
       <c r="R287" t="n">
-        <v>7330285</v>
+        <v>7330337</v>
       </c>
       <c r="S287" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD287" t="b">
@@ -32393,12 +32393,12 @@
       <c r="AT287" t="inlineStr"/>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -32409,10 +32409,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>135356866</v>
+        <v>135353550</v>
       </c>
       <c r="B288" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -32420,34 +32420,34 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>599543</v>
+        <v>599776</v>
       </c>
       <c r="R288" t="n">
-        <v>7330151</v>
+        <v>7330285</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -32479,7 +32479,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD288" t="b">
@@ -32504,12 +32504,12 @@
       <c r="AT288" t="inlineStr"/>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -32520,10 +32520,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>135357158</v>
+        <v>135356866</v>
       </c>
       <c r="B289" t="n">
-        <v>92245</v>
+        <v>79396</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32531,37 +32531,37 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>658</v>
+        <v>260591</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>599761</v>
+        <v>599543</v>
       </c>
       <c r="R289" t="n">
-        <v>7330625</v>
+        <v>7330151</v>
       </c>
       <c r="S289" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -32600,7 +32600,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD289" t="b">
@@ -32615,12 +32615,12 @@
       <c r="AT289" t="inlineStr"/>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -32631,7 +32631,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>135357166</v>
+        <v>135357158</v>
       </c>
       <c r="B290" t="n">
         <v>92245</v>
@@ -32666,10 +32666,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>599469</v>
+        <v>599761</v>
       </c>
       <c r="R290" t="n">
-        <v>7330869</v>
+        <v>7330625</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -32701,7 +32701,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD290" t="b">
@@ -32742,7 +32742,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>135358328</v>
+        <v>135357166</v>
       </c>
       <c r="B291" t="n">
         <v>92245</v>
@@ -32773,17 +32773,17 @@
       <c r="I291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>599965</v>
+        <v>599469</v>
       </c>
       <c r="R291" t="n">
-        <v>7330859</v>
+        <v>7330869</v>
       </c>
       <c r="S291" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -32822,7 +32822,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD291" t="b">
@@ -32837,12 +32837,12 @@
       <c r="AT291" t="inlineStr"/>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -32853,10 +32853,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>135358316</v>
+        <v>135358328</v>
       </c>
       <c r="B292" t="n">
-        <v>91970</v>
+        <v>92245</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32864,21 +32864,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -32888,10 +32888,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>599836</v>
+        <v>599965</v>
       </c>
       <c r="R292" t="n">
-        <v>7330649</v>
+        <v>7330859</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -32923,7 +32923,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -32933,7 +32933,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD292" t="b">
@@ -32964,7 +32964,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>135358324</v>
+        <v>135358316</v>
       </c>
       <c r="B293" t="n">
         <v>91970</v>
@@ -32999,10 +32999,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>599960</v>
+        <v>599836</v>
       </c>
       <c r="R293" t="n">
-        <v>7330832</v>
+        <v>7330649</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -33034,7 +33034,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -33044,7 +33044,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD293" t="b">
@@ -33075,10 +33075,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>135357161</v>
+        <v>135358324</v>
       </c>
       <c r="B294" t="n">
-        <v>91974</v>
+        <v>91970</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33086,37 +33086,37 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>599676</v>
+        <v>599960</v>
       </c>
       <c r="R294" t="n">
-        <v>7330713</v>
+        <v>7330832</v>
       </c>
       <c r="S294" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -33155,7 +33155,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD294" t="b">
@@ -33170,12 +33170,12 @@
       <c r="AT294" t="inlineStr"/>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
@@ -33186,7 +33186,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>135357162</v>
+        <v>135357161</v>
       </c>
       <c r="B295" t="n">
         <v>91974</v>
@@ -33221,10 +33221,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>599589</v>
+        <v>599676</v>
       </c>
       <c r="R295" t="n">
-        <v>7330732</v>
+        <v>7330713</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -33256,7 +33256,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD295" t="b">
@@ -33297,7 +33297,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>135357164</v>
+        <v>135357162</v>
       </c>
       <c r="B296" t="n">
         <v>91974</v>
@@ -33332,10 +33332,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>599528</v>
+        <v>599589</v>
       </c>
       <c r="R296" t="n">
-        <v>7330783</v>
+        <v>7330732</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -33367,7 +33367,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -33377,7 +33377,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD296" t="b">
@@ -33408,7 +33408,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>135358318</v>
+        <v>135357164</v>
       </c>
       <c r="B297" t="n">
         <v>91974</v>
@@ -33439,14 +33439,14 @@
       <c r="I297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>599930</v>
+        <v>599528</v>
       </c>
       <c r="R297" t="n">
-        <v>7330683</v>
+        <v>7330783</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -33478,7 +33478,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD297" t="b">
@@ -33503,12 +33503,12 @@
       <c r="AT297" t="inlineStr"/>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
@@ -33519,7 +33519,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>135358327</v>
+        <v>135358318</v>
       </c>
       <c r="B298" t="n">
         <v>91974</v>
@@ -33554,13 +33554,13 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>599974</v>
+        <v>599930</v>
       </c>
       <c r="R298" t="n">
-        <v>7330848</v>
+        <v>7330683</v>
       </c>
       <c r="S298" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -33599,7 +33599,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD298" t="b">
@@ -33630,48 +33630,48 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>135357167</v>
+        <v>135358327</v>
       </c>
       <c r="B299" t="n">
-        <v>91988</v>
+        <v>91974</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>599463</v>
+        <v>599974</v>
       </c>
       <c r="R299" t="n">
-        <v>7330869</v>
+        <v>7330848</v>
       </c>
       <c r="S299" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD299" t="b">
@@ -33725,12 +33725,12 @@
       <c r="AT299" t="inlineStr"/>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -33741,32 +33741,32 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>135357160</v>
+        <v>135357167</v>
       </c>
       <c r="B300" t="n">
-        <v>92406</v>
+        <v>91988</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -33776,10 +33776,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>599676</v>
+        <v>599463</v>
       </c>
       <c r="R300" t="n">
-        <v>7330713</v>
+        <v>7330869</v>
       </c>
       <c r="S300" t="n">
         <v>10</v>
@@ -33811,7 +33811,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD300" t="b">
@@ -33852,10 +33852,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>135358317</v>
+        <v>135357160</v>
       </c>
       <c r="B301" t="n">
-        <v>83222</v>
+        <v>92406</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33863,37 +33863,37 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>599871</v>
+        <v>599676</v>
       </c>
       <c r="R301" t="n">
-        <v>7330715</v>
+        <v>7330713</v>
       </c>
       <c r="S301" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -33932,7 +33932,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD301" t="b">
@@ -33941,19 +33941,18 @@
       <c r="AE301" t="b">
         <v>0</v>
       </c>
-      <c r="AF301" t="inlineStr"/>
       <c r="AG301" t="b">
         <v>0</v>
       </c>
       <c r="AT301" t="inlineStr"/>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -33964,48 +33963,48 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>135353570</v>
+        <v>135358317</v>
       </c>
       <c r="B302" t="n">
-        <v>92153</v>
+        <v>83222</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>599487</v>
+        <v>599871</v>
       </c>
       <c r="R302" t="n">
-        <v>7330893</v>
+        <v>7330715</v>
       </c>
       <c r="S302" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -34034,7 +34033,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -34044,7 +34043,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD302" t="b">
@@ -34053,18 +34052,19 @@
       <c r="AE302" t="b">
         <v>0</v>
       </c>
+      <c r="AF302" t="inlineStr"/>
       <c r="AG302" t="b">
         <v>0</v>
       </c>
       <c r="AT302" t="inlineStr"/>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
@@ -34075,48 +34075,48 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>135358321</v>
+        <v>135353570</v>
       </c>
       <c r="B303" t="n">
-        <v>96037</v>
+        <v>92153</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>2387</v>
+        <v>1503</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>599988</v>
+        <v>599487</v>
       </c>
       <c r="R303" t="n">
-        <v>7330863</v>
+        <v>7330893</v>
       </c>
       <c r="S303" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -34155,7 +34155,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD303" t="b">
@@ -34170,12 +34170,12 @@
       <c r="AT303" t="inlineStr"/>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -34186,48 +34186,48 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>135354303</v>
+        <v>135358321</v>
       </c>
       <c r="B304" t="n">
-        <v>79373</v>
+        <v>96037</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
         <is>
-          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>599499</v>
+        <v>599988</v>
       </c>
       <c r="R304" t="n">
-        <v>7330997</v>
+        <v>7330863</v>
       </c>
       <c r="S304" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -34266,7 +34266,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD304" t="b">
@@ -34281,12 +34281,12 @@
       <c r="AT304" t="inlineStr"/>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -34297,48 +34297,48 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>135356874</v>
+        <v>135354303</v>
       </c>
       <c r="B305" t="n">
-        <v>80382</v>
+        <v>79373</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Tors Gr 2 (N)-3 (S)_Muorkenåive-Ássjátj_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>599554</v>
+        <v>599499</v>
       </c>
       <c r="R305" t="n">
-        <v>7330507</v>
+        <v>7330997</v>
       </c>
       <c r="S305" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -34377,7 +34377,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD305" t="b">
@@ -34392,12 +34392,12 @@
       <c r="AT305" t="inlineStr"/>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
@@ -34408,10 +34408,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>135353564</v>
+        <v>135356874</v>
       </c>
       <c r="B306" t="n">
-        <v>80492</v>
+        <v>80382</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -34419,34 +34419,34 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>599826</v>
+        <v>599554</v>
       </c>
       <c r="R306" t="n">
-        <v>7330870</v>
+        <v>7330507</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -34478,7 +34478,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -34488,7 +34488,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD306" t="b">
@@ -34503,12 +34503,12 @@
       <c r="AT306" t="inlineStr"/>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -34519,53 +34519,48 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>135353563</v>
+        <v>135353564</v>
       </c>
       <c r="B307" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P307" t="inlineStr">
         <is>
           <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>599878</v>
+        <v>599826</v>
       </c>
       <c r="R307" t="n">
         <v>7330870</v>
       </c>
       <c r="S307" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -34594,7 +34589,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -34604,7 +34599,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD307" t="b">
@@ -34635,7 +34630,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>135353567</v>
+        <v>135353563</v>
       </c>
       <c r="B308" t="n">
         <v>57975</v>
@@ -34675,13 +34670,13 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>599682</v>
+        <v>599878</v>
       </c>
       <c r="R308" t="n">
-        <v>7330899</v>
+        <v>7330870</v>
       </c>
       <c r="S308" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -34710,7 +34705,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -34720,7 +34715,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD308" t="b">
@@ -34751,7 +34746,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>135353571</v>
+        <v>135353567</v>
       </c>
       <c r="B309" t="n">
         <v>57975</v>
@@ -34782,7 +34777,7 @@
       <c r="I309" t="inlineStr"/>
       <c r="M309" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -34791,10 +34786,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>599393</v>
+        <v>599682</v>
       </c>
       <c r="R309" t="n">
-        <v>7330851</v>
+        <v>7330899</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -34826,7 +34821,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -34836,7 +34831,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD309" t="b">
@@ -34867,7 +34862,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>135356381</v>
+        <v>135353571</v>
       </c>
       <c r="B310" t="n">
         <v>57975</v>
@@ -34896,27 +34891,24 @@
         </is>
       </c>
       <c r="I310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
-      <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>599631</v>
+        <v>599393</v>
       </c>
       <c r="R310" t="n">
-        <v>7330482</v>
+        <v>7330851</v>
       </c>
       <c r="S310" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -34945,7 +34937,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -34955,19 +34947,14 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD310" t="b">
         <v>0</v>
       </c>
       <c r="AE310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -34975,12 +34962,12 @@
       <c r="AT310" t="inlineStr"/>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
@@ -34991,7 +34978,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>135357157</v>
+        <v>135356381</v>
       </c>
       <c r="B311" t="n">
         <v>57975</v>
@@ -35034,13 +35021,13 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>599738</v>
+        <v>599631</v>
       </c>
       <c r="R311" t="n">
-        <v>7330532</v>
+        <v>7330482</v>
       </c>
       <c r="S311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -35069,7 +35056,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -35079,19 +35066,19 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD311" t="b">
         <v>0</v>
       </c>
       <c r="AE311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -35099,12 +35086,12 @@
       <c r="AT311" t="inlineStr"/>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -35115,10 +35102,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>135353553</v>
+        <v>135357157</v>
       </c>
       <c r="B312" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -35126,42 +35113,45 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr"/>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>600002</v>
+        <v>599738</v>
       </c>
       <c r="R312" t="n">
-        <v>7330496</v>
+        <v>7330532</v>
       </c>
       <c r="S312" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -35190,7 +35180,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -35200,7 +35190,12 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC312" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD312" t="b">
@@ -35215,12 +35210,12 @@
       <c r="AT312" t="inlineStr"/>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
@@ -35231,7 +35226,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>135357159</v>
+        <v>135353553</v>
       </c>
       <c r="B313" t="n">
         <v>58136</v>
@@ -35260,27 +35255,24 @@
         </is>
       </c>
       <c r="I313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>599753</v>
+        <v>600002</v>
       </c>
       <c r="R313" t="n">
-        <v>7330627</v>
+        <v>7330496</v>
       </c>
       <c r="S313" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -35309,7 +35301,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -35319,12 +35311,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD313" t="b">
@@ -35339,12 +35326,12 @@
       <c r="AT313" t="inlineStr"/>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -35355,48 +35342,56 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>135356873</v>
+        <v>135357159</v>
       </c>
       <c r="B314" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>599575</v>
+        <v>599753</v>
       </c>
       <c r="R314" t="n">
-        <v>7330476</v>
+        <v>7330627</v>
       </c>
       <c r="S314" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -35425,7 +35420,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -35435,7 +35430,12 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD314" t="b">
@@ -35450,12 +35450,12 @@
       <c r="AT314" t="inlineStr"/>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
@@ -35466,10 +35466,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>135353565</v>
+        <v>135356873</v>
       </c>
       <c r="B315" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -35477,34 +35477,34 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>599694</v>
+        <v>599575</v>
       </c>
       <c r="R315" t="n">
-        <v>7330869</v>
+        <v>7330476</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -35536,7 +35536,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -35546,7 +35546,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD315" t="b">
@@ -35561,12 +35561,12 @@
       <c r="AT315" t="inlineStr"/>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -35577,7 +35577,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>135353568</v>
+        <v>135353565</v>
       </c>
       <c r="B316" t="n">
         <v>99217</v>
@@ -35612,10 +35612,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>599518</v>
+        <v>599694</v>
       </c>
       <c r="R316" t="n">
-        <v>7330920</v>
+        <v>7330869</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -35647,7 +35647,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -35657,7 +35657,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD316" t="b">
@@ -35688,7 +35688,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>135356875</v>
+        <v>135353568</v>
       </c>
       <c r="B317" t="n">
         <v>99217</v>
@@ -35719,14 +35719,14 @@
       <c r="I317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>599368</v>
+        <v>599518</v>
       </c>
       <c r="R317" t="n">
-        <v>7330524</v>
+        <v>7330920</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -35758,7 +35758,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -35768,7 +35768,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -35783,12 +35783,12 @@
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
@@ -35799,7 +35799,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>135357165</v>
+        <v>135356875</v>
       </c>
       <c r="B318" t="n">
         <v>99217</v>
@@ -35830,17 +35830,17 @@
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>599501</v>
+        <v>599368</v>
       </c>
       <c r="R318" t="n">
-        <v>7330822</v>
+        <v>7330524</v>
       </c>
       <c r="S318" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -35879,7 +35879,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -35894,12 +35894,12 @@
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
@@ -35910,7 +35910,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>135358325</v>
+        <v>135357165</v>
       </c>
       <c r="B319" t="n">
         <v>99217</v>
@@ -35941,14 +35941,14 @@
       <c r="I319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>599968</v>
+        <v>599501</v>
       </c>
       <c r="R319" t="n">
-        <v>7330829</v>
+        <v>7330822</v>
       </c>
       <c r="S319" t="n">
         <v>10</v>
@@ -35980,7 +35980,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -36005,12 +36005,12 @@
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
@@ -36021,7 +36021,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>135358329</v>
+        <v>135358325</v>
       </c>
       <c r="B320" t="n">
         <v>99217</v>
@@ -36056,13 +36056,13 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>599960</v>
+        <v>599968</v>
       </c>
       <c r="R320" t="n">
-        <v>7330852</v>
+        <v>7330829</v>
       </c>
       <c r="S320" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -36101,7 +36101,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -36132,7 +36132,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>135362167</v>
+        <v>135358329</v>
       </c>
       <c r="B321" t="n">
         <v>99217</v>
@@ -36163,17 +36163,17 @@
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>599652</v>
+        <v>599960</v>
       </c>
       <c r="R321" t="n">
-        <v>7330526</v>
+        <v>7330852</v>
       </c>
       <c r="S321" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -36200,9 +36200,19 @@
           <t>2026-07-23</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -36217,12 +36227,12 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Sofia Fransén</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -36233,10 +36243,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>135357153</v>
+        <v>135362167</v>
       </c>
       <c r="B322" t="n">
-        <v>102871</v>
+        <v>99217</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36244,21 +36254,21 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>223037</v>
+        <v>221952</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I322" t="inlineStr"/>
@@ -36268,13 +36278,13 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>599578</v>
+        <v>599652</v>
       </c>
       <c r="R322" t="n">
-        <v>7330454</v>
+        <v>7330526</v>
       </c>
       <c r="S322" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -36301,19 +36311,9 @@
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA322" t="inlineStr">
         <is>
           <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>13:24</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36328,12 +36328,12 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sofia Fransén</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -36344,10 +36344,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>135357154</v>
+        <v>135357153</v>
       </c>
       <c r="B323" t="n">
-        <v>101293</v>
+        <v>102871</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36355,21 +36355,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>224885</v>
+        <v>223037</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
@@ -36455,7 +36455,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>135358315</v>
+        <v>135357154</v>
       </c>
       <c r="B324" t="n">
         <v>101293</v>
@@ -36486,17 +36486,17 @@
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Muorkenåive S, Pi lm</t>
+          <t>Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>599572</v>
+        <v>599578</v>
       </c>
       <c r="R324" t="n">
-        <v>7330459</v>
+        <v>7330454</v>
       </c>
       <c r="S324" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -36525,7 +36525,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -36535,7 +36535,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36550,12 +36550,12 @@
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -36566,7 +36566,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>135358323</v>
+        <v>135358315</v>
       </c>
       <c r="B325" t="n">
         <v>101293</v>
@@ -36601,10 +36601,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>599957</v>
+        <v>599572</v>
       </c>
       <c r="R325" t="n">
-        <v>7330879</v>
+        <v>7330459</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -36636,7 +36636,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -36646,7 +36646,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD325" t="b">
@@ -36677,32 +36677,32 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>135358330</v>
+        <v>135358323</v>
       </c>
       <c r="B326" t="n">
-        <v>79396</v>
+        <v>101293</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>260591</v>
+        <v>224885</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I326" t="inlineStr"/>
@@ -36712,13 +36712,13 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>599483</v>
+        <v>599957</v>
       </c>
       <c r="R326" t="n">
-        <v>7330912</v>
+        <v>7330879</v>
       </c>
       <c r="S326" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD326" t="b">
@@ -36788,10 +36788,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>135351898</v>
+        <v>135358330</v>
       </c>
       <c r="B327" t="n">
-        <v>79452</v>
+        <v>79396</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -36799,37 +36799,37 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>864</v>
+        <v>260591</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
         <is>
-          <t>N Muorkenåive-Ássjátj, Pi lm</t>
+          <t>Muorkenåive S, Pi lm</t>
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>600023</v>
+        <v>599483</v>
       </c>
       <c r="R327" t="n">
-        <v>7331182</v>
+        <v>7330912</v>
       </c>
       <c r="S327" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -36868,7 +36868,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD327" t="b">
@@ -36883,12 +36883,12 @@
       <c r="AT327" t="inlineStr"/>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -36899,48 +36899,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>135353558</v>
+        <v>135351898</v>
       </c>
       <c r="B328" t="n">
-        <v>79373</v>
+        <v>79452</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Muorkenåive, Pi lm</t>
+          <t>N Muorkenåive-Ássjátj, Pi lm</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>600102</v>
+        <v>600023</v>
       </c>
       <c r="R328" t="n">
-        <v>7330759</v>
+        <v>7331182</v>
       </c>
       <c r="S328" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -36979,7 +36979,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD328" t="b">
@@ -36994,12 +36994,12 @@
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -37010,50 +37010,45 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>135353557</v>
+        <v>135353558</v>
       </c>
       <c r="B329" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P329" t="inlineStr">
         <is>
           <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>600107</v>
+        <v>600102</v>
       </c>
       <c r="R329" t="n">
-        <v>7330755</v>
+        <v>7330759</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -37085,7 +37080,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -37095,7 +37090,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD329" t="b">
@@ -37126,7 +37121,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>135353560</v>
+        <v>135353557</v>
       </c>
       <c r="B330" t="n">
         <v>57975</v>
@@ -37166,10 +37161,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>600101</v>
+        <v>600107</v>
       </c>
       <c r="R330" t="n">
-        <v>7330764</v>
+        <v>7330755</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -37201,7 +37196,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -37211,7 +37206,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -37242,7 +37237,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>135353561</v>
+        <v>135353560</v>
       </c>
       <c r="B331" t="n">
         <v>57975</v>
@@ -37282,10 +37277,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>600081</v>
+        <v>600101</v>
       </c>
       <c r="R331" t="n">
-        <v>7330796</v>
+        <v>7330764</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -37317,7 +37312,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -37327,7 +37322,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -37358,45 +37353,50 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>135353555</v>
+        <v>135353561</v>
       </c>
       <c r="B332" t="n">
-        <v>101293</v>
+        <v>57975</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>224885</v>
+        <v>100109</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P332" t="inlineStr">
         <is>
           <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>600092</v>
+        <v>600081</v>
       </c>
       <c r="R332" t="n">
-        <v>7330734</v>
+        <v>7330796</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -37428,7 +37428,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -37438,7 +37438,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -37469,45 +37469,45 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>135350679</v>
+        <v>135353555</v>
       </c>
       <c r="B333" t="n">
-        <v>78393</v>
+        <v>101293</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>314</v>
+        <v>224885</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Muorkenåive N, Pi lm</t>
+          <t>Muorkenåive, Pi lm</t>
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>600102</v>
+        <v>600092</v>
       </c>
       <c r="R333" t="n">
-        <v>7331208</v>
+        <v>7330734</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -37539,7 +37539,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -37549,7 +37549,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -37564,12 +37564,12 @@
       <c r="AT333" t="inlineStr"/>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
@@ -37580,32 +37580,32 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>135350592</v>
+        <v>135350679</v>
       </c>
       <c r="B334" t="n">
-        <v>79452</v>
+        <v>78393</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -37615,10 +37615,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>600105</v>
+        <v>600102</v>
       </c>
       <c r="R334" t="n">
-        <v>7331205</v>
+        <v>7331208</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -37650,7 +37650,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -37660,7 +37660,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -37691,7 +37691,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>135350677</v>
+        <v>135350592</v>
       </c>
       <c r="B335" t="n">
         <v>79452</v>
@@ -37726,10 +37726,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>600100</v>
+        <v>600105</v>
       </c>
       <c r="R335" t="n">
-        <v>7331204</v>
+        <v>7331205</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -37761,7 +37761,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -37771,7 +37771,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -37802,10 +37802,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>135350680</v>
+        <v>135350677</v>
       </c>
       <c r="B336" t="n">
-        <v>83363</v>
+        <v>79452</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -37813,21 +37813,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I336" t="inlineStr"/>
@@ -37872,7 +37872,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -37882,7 +37882,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -37913,32 +37913,32 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>135350590</v>
+        <v>135350680</v>
       </c>
       <c r="B337" t="n">
-        <v>92320</v>
+        <v>83363</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>2063</v>
+        <v>1467</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr"/>
@@ -37948,13 +37948,13 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>600137</v>
+        <v>600100</v>
       </c>
       <c r="R337" t="n">
-        <v>7331217</v>
+        <v>7331204</v>
       </c>
       <c r="S337" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -37993,7 +37993,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -38024,32 +38024,32 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>135350593</v>
+        <v>135350590</v>
       </c>
       <c r="B338" t="n">
-        <v>80493</v>
+        <v>92320</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>6462</v>
+        <v>2063</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I338" t="inlineStr"/>
@@ -38059,10 +38059,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>600068</v>
+        <v>600137</v>
       </c>
       <c r="R338" t="n">
-        <v>7331214</v>
+        <v>7331217</v>
       </c>
       <c r="S338" t="n">
         <v>7</v>
@@ -38094,7 +38094,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -38104,7 +38104,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -38128,6 +38128,117 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>135350593</v>
+      </c>
+      <c r="B339" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr"/>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>Muorkenåive N, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q339" t="n">
+        <v>600068</v>
+      </c>
+      <c r="R339" t="n">
+        <v>7331214</v>
+      </c>
+      <c r="S339" t="n">
+        <v>7</v>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG339" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT339" t="inlineStr"/>
+      <c r="AW339" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX339" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY339" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -37680,7 +37680,7 @@
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
@@ -37791,7 +37791,7 @@
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -38013,7 +38013,7 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne  Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -16965,7 +16965,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -37902,7 +37902,7 @@
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -17230,7 +17230,7 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Anton Lundberg, Alva Dahlqvist Cederstrand</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -38167,7 +38167,7 @@
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -20990,6 +20990,10 @@
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
           <t>Muorkenåive S, Pi lm</t>
@@ -21048,8 +21052,9 @@
         <v>0</v>
       </c>
       <c r="AE183" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY342"/>
+  <dimension ref="A1:AZ342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356375</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357129</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353493</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353498</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356848</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358272</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358273</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358280</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356374</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2117,6 +2182,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382715</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2228,6 +2298,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382714</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356212</t>
         </is>
       </c>
     </row>
@@ -2492,6 +2572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135420258</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356208</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2714,6 +2804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357125</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2825,6 +2920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357124</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2936,6 +3036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356210</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3047,6 +3152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356372</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3158,6 +3268,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353495</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3269,6 +3384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356837</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3380,6 +3500,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356841</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3491,6 +3616,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357126</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3607,6 +3737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353488</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3723,6 +3858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353503</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3847,6 +3987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356376</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3963,6 +4108,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357127</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4079,6 +4229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358283</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4198,6 +4353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382711</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4309,6 +4469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384162</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4420,6 +4585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356843</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4531,6 +4701,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358269</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4642,6 +4817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353491</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4753,6 +4933,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356209</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4864,6 +5049,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356839</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4975,6 +5165,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358270</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5086,6 +5281,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356206</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5197,6 +5397,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356845</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5308,6 +5513,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358281</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5419,6 +5629,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353486</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5530,6 +5745,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353494</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5641,6 +5861,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353497</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5752,6 +5977,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356211</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5863,6 +6093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356213</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5974,6 +6209,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356844</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6085,6 +6325,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356846</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6196,6 +6441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353490</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6295,6 +6545,11 @@
       <c r="AY51" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362160</t>
         </is>
       </c>
     </row>
@@ -6413,6 +6668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358271</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6524,6 +6784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356838</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6635,6 +6900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357123</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6746,6 +7016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382713</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6857,6 +7132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357122</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6968,6 +7248,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357120</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7079,6 +7364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358268</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7190,6 +7480,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358284</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7301,6 +7596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382388</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7410,6 +7710,11 @@
       <c r="AY61" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382712</t>
         </is>
       </c>
     </row>
@@ -7524,6 +7829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357130</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7635,6 +7945,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356244</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7746,6 +8061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356883</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7857,6 +8177,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356888</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7968,6 +8293,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356887</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8079,6 +8409,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356242</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8190,6 +8525,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357194</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8301,6 +8641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379282</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8412,6 +8757,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379283</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8523,6 +8873,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385142</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8634,6 +8989,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356239</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8745,6 +9105,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357197</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8856,6 +9221,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357203</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8967,6 +9337,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357207</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9078,6 +9453,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357208</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9189,6 +9569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382719</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9300,6 +9685,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356240</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9411,6 +9801,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382464</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9522,6 +9917,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382466</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9633,6 +10033,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384252</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9757,6 +10162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382716</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9881,6 +10291,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382779</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10005,6 +10420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384126</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10129,6 +10549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357215</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10240,6 +10665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382469</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10351,6 +10781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384124</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10462,6 +10897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356241</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10573,6 +11013,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357201</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10684,6 +11129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357211</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10795,6 +11245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357212</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10906,6 +11361,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358340</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11017,6 +11477,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358342</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11128,6 +11593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382720</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11239,6 +11709,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382723</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11350,6 +11825,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356886</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11461,6 +11941,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356243</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11572,6 +12057,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356884</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11683,6 +12173,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382031</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11794,6 +12289,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382032</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11905,6 +12405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384245</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12016,6 +12521,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384249</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12127,6 +12637,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382721</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12238,6 +12753,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384251</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12349,6 +12869,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357209</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12460,6 +12985,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357202</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12571,6 +13101,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382724</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12682,6 +13217,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357195</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12793,6 +13333,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357198</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12904,6 +13449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382718</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13015,6 +13565,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357196</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13126,6 +13681,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357199</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13237,6 +13797,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357205</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13348,6 +13913,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357206</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13459,6 +14029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357213</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13570,6 +14145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358341</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13681,6 +14261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382717</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13792,6 +14377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382722</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13904,6 +14494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356859</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14015,6 +14610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353510</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14126,6 +14726,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353501</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14237,6 +14842,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353508</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14348,6 +14958,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353519</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14459,6 +15074,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353522</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14570,6 +15190,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353525</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14681,6 +15306,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356379</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14792,6 +15422,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356849</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14903,6 +15538,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356851</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15014,6 +15654,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356854</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15125,6 +15770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357135</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15236,6 +15886,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358290</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15347,6 +16002,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358300</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15458,6 +16118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382781</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15569,6 +16234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353499</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15680,6 +16350,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353520</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15791,6 +16466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382780</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15902,6 +16582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353502</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16013,6 +16698,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356215</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16124,6 +16814,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356221</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16235,6 +16930,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356847</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16346,6 +17046,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358294</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16457,6 +17162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353523</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16568,6 +17278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356220</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16679,6 +17394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356850</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16790,6 +17510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357150</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16901,6 +17626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358297</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17012,6 +17742,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358304</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17121,6 +17856,11 @@
       <c r="AY148" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353517</t>
         </is>
       </c>
     </row>
@@ -17238,6 +17978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356378</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17349,6 +18094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356861</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17460,6 +18210,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353524</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17571,6 +18326,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358288</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17682,6 +18442,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358298</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17793,6 +18558,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356223</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17904,6 +18674,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356224</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18015,6 +18790,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356857</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18126,6 +18906,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353500</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18237,6 +19022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356853</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18348,6 +19138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357133</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18459,6 +19254,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357142</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18570,6 +19370,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382782</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18681,6 +19486,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356855</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18792,6 +19602,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353513</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18903,6 +19718,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353515</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19014,6 +19834,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353526</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19125,6 +19950,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353529</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19236,6 +20066,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353534</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19337,6 +20172,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362165</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19448,6 +20288,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353509</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19559,6 +20404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353530</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19670,6 +20520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353535</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19781,6 +20636,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356222</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19892,6 +20752,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358306</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20003,6 +20868,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358308</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20119,6 +20989,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353531</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20235,6 +21110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353533</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20351,6 +21231,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356216</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20475,6 +21360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356380</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20599,6 +21489,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357148</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20723,6 +21618,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357151</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20847,6 +21747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357152</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20956,6 +21861,11 @@
       <c r="AY182" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353537</t>
         </is>
       </c>
     </row>
@@ -21074,6 +21984,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135361173</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21185,6 +22100,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353512</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21296,6 +22216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353528</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21407,6 +22332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357137</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21518,6 +22448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357141</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21629,6 +22564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358292</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21740,6 +22680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358295</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21851,6 +22796,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358307</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21962,6 +22912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356218</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22073,6 +23028,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358287</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22184,6 +23144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353521</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22295,6 +23260,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353527</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22406,6 +23376,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356856</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22517,6 +23492,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356858</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22628,6 +23608,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356860</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22739,6 +23724,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356862</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22840,6 +23830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362163</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22951,6 +23946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357136</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23062,6 +24062,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357146</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23173,6 +24178,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357145</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23284,6 +24294,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358296</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23395,6 +24410,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357138</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23506,6 +24526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357140</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23617,6 +24642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357147</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23728,6 +24758,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358293</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23839,6 +24874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358302</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23950,6 +24990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358310</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24062,6 +25107,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356852</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24174,6 +25224,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357134</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24271,6 +25326,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91798</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24368,6 +25428,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/215318</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24479,6 +25544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353573</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24576,6 +25646,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/302676</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24673,6 +25748,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/405628</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24784,6 +25864,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350748</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24895,6 +25980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353572</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25006,6 +26096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357173</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25103,6 +26198,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/334447</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25200,6 +26300,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/376098</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25297,6 +26402,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/385987</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25394,6 +26504,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/520073</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25505,6 +26620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357185</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25602,6 +26722,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/414990</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25713,6 +26838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357176</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25810,6 +26940,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1120620</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25907,6 +27042,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1886847</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26018,6 +27158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353574</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26129,6 +27274,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356234</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26240,6 +27390,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356383</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26351,6 +27506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357168</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26452,6 +27612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362174</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26553,6 +27718,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362172</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26677,6 +27847,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356382</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26793,6 +27968,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358333</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26904,6 +28084,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356235</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27028,6 +28213,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357184</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27139,6 +28329,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356384</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27250,6 +28445,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356879</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27361,6 +28561,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356880</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27472,6 +28677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382462</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27583,6 +28793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356881</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27694,6 +28909,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357170</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27805,6 +29025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357172</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27916,6 +29141,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357187</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28013,6 +29243,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4043291</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28124,6 +29359,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353575</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28235,6 +29475,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357179</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28346,6 +29591,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358332</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28457,6 +29707,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353577</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28568,6 +29823,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356877</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28679,6 +29939,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357180</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28790,6 +30055,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357193</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28891,6 +30161,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362173</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29002,6 +30277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135383915</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29113,6 +30393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357178</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29224,6 +30509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357190</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29335,6 +30625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357169</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29446,6 +30741,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357177</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29557,6 +30857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357182</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29668,6 +30973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357183</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29779,6 +31089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357186</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29890,6 +31205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357188</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30001,6 +31321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357191</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30113,6 +31438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353538</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30224,6 +31554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356867</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30335,6 +31670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353549</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30446,6 +31786,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356231</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30557,6 +31902,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356870</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30668,6 +32018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353541</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30779,6 +32134,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356227</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30890,6 +32250,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356228</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -31001,6 +32366,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353539</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -31112,6 +32482,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353545</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -31223,6 +32598,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356865</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31334,6 +32714,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353540</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -31445,6 +32830,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356868</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31556,6 +32946,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356869</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31672,6 +33067,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353547</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31788,6 +33188,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356230</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31899,6 +33304,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353543</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -32010,6 +33420,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356871</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -32121,6 +33536,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356863</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -32232,6 +33652,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353546</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32343,6 +33768,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353551</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32454,6 +33884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356226</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32565,6 +34000,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356229</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32676,6 +34116,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356864</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32787,6 +34232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358313</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32898,6 +34348,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353550</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -33009,6 +34464,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356866</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -33120,6 +34580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357158</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33231,6 +34696,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357166</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33342,6 +34812,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358328</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33453,6 +34928,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358316</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33564,6 +35044,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358324</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33675,6 +35160,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357161</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33786,6 +35276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357162</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33897,6 +35392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357164</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -34008,6 +35508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358318</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -34119,6 +35624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358327</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34230,6 +35740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357167</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34341,6 +35856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357160</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34453,6 +35973,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358317</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34564,6 +36089,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353570</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34675,6 +36205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358321</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34786,6 +36321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354303</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34897,6 +36437,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356874</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -35008,6 +36553,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353564</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -35124,6 +36674,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353563</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -35240,6 +36795,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353567</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35356,6 +36916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353571</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35480,6 +37045,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356381</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35604,6 +37174,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357157</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35720,6 +37295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353553</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35844,6 +37424,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357159</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35955,6 +37540,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356873</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -36066,6 +37656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353565</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -36177,6 +37772,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353568</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36288,6 +37888,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356875</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36399,6 +38004,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357165</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36510,6 +38120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358325</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36621,6 +38236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358329</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36722,6 +38342,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135362167</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36833,6 +38458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357153</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36944,6 +38574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357154</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -37055,6 +38690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358315</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -37166,6 +38806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358323</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37277,6 +38922,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358330</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37388,6 +39038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351898</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37499,6 +39154,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353558</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37615,6 +39275,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353557</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37731,6 +39396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353560</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37847,6 +39517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353561</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37958,6 +39633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135353555</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -38069,6 +39749,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350679</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -38180,6 +39865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350592</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38291,6 +39981,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350677</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38402,6 +40097,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350680</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38513,6 +40213,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350590</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -38624,8 +40329,356 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135350593</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135356842</v>
       </c>
       <c r="B2" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135356375</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135356889</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135357129</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135353493</v>
       </c>
       <c r="B6" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>135353492</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>135353498</v>
       </c>
       <c r="B8" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135356848</v>
       </c>
       <c r="B9" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135358272</v>
       </c>
       <c r="B10" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135358273</v>
       </c>
       <c r="B11" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135358280</v>
       </c>
       <c r="B12" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>135356374</v>
       </c>
       <c r="B13" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135382715</v>
       </c>
       <c r="B14" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>135382714</v>
       </c>
       <c r="B15" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135356212</v>
       </c>
       <c r="B16" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135420258</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>135356208</v>
       </c>
       <c r="B18" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135357125</v>
       </c>
       <c r="B19" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135357124</v>
       </c>
       <c r="B20" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135356210</v>
       </c>
       <c r="B21" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135356372</v>
       </c>
       <c r="B22" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135353495</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>135356837</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>135356841</v>
       </c>
       <c r="B25" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>135357126</v>
       </c>
       <c r="B26" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>135353488</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>135353503</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>135356376</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>135357127</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>135358283</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>135382711</v>
       </c>
       <c r="B32" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>135384162</v>
       </c>
       <c r="B33" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>135356843</v>
       </c>
       <c r="B34" t="n">
-        <v>99099</v>
+        <v>99146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135358269</v>
       </c>
       <c r="B35" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135353491</v>
       </c>
       <c r="B36" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>135356209</v>
       </c>
       <c r="B37" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135356839</v>
       </c>
       <c r="B38" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135358270</v>
       </c>
       <c r="B39" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135356206</v>
       </c>
       <c r="B40" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>135356845</v>
       </c>
       <c r="B41" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>135358281</v>
       </c>
       <c r="B42" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>135353486</v>
       </c>
       <c r="B43" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>135353494</v>
       </c>
       <c r="B44" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>135353497</v>
       </c>
       <c r="B45" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>135356211</v>
       </c>
       <c r="B46" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>135356213</v>
       </c>
       <c r="B47" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>135356844</v>
       </c>
       <c r="B48" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>135356846</v>
       </c>
       <c r="B49" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135353490</v>
       </c>
       <c r="B50" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>135362160</v>
       </c>
       <c r="B51" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>135358271</v>
       </c>
       <c r="B52" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>135356838</v>
       </c>
       <c r="B53" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>135357123</v>
       </c>
       <c r="B54" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>135382713</v>
       </c>
       <c r="B55" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>135357122</v>
       </c>
       <c r="B56" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135357120</v>
       </c>
       <c r="B57" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>135358268</v>
       </c>
       <c r="B58" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>135358284</v>
       </c>
       <c r="B59" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>135382388</v>
       </c>
       <c r="B60" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>135382712</v>
       </c>
       <c r="B61" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>135357130</v>
       </c>
       <c r="B62" t="n">
-        <v>101952</v>
+        <v>102000</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>135356244</v>
       </c>
       <c r="B63" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>135356883</v>
       </c>
       <c r="B64" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>135356888</v>
       </c>
       <c r="B65" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>135356887</v>
       </c>
       <c r="B66" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135356242</v>
       </c>
       <c r="B67" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>135357194</v>
       </c>
       <c r="B68" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135379282</v>
       </c>
       <c r="B69" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135379283</v>
       </c>
       <c r="B70" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>135385142</v>
       </c>
       <c r="B71" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>135356239</v>
       </c>
       <c r="B72" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>135357197</v>
       </c>
       <c r="B73" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>135357203</v>
       </c>
       <c r="B74" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135357207</v>
       </c>
       <c r="B75" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>135357208</v>
       </c>
       <c r="B76" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>135382719</v>
       </c>
       <c r="B77" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>135356240</v>
       </c>
       <c r="B78" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>135382464</v>
       </c>
       <c r="B79" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>135382466</v>
       </c>
       <c r="B80" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>135384252</v>
       </c>
       <c r="B81" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>135382716</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>135382779</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>135384126</v>
       </c>
       <c r="B84" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>135357215</v>
       </c>
       <c r="B85" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>135382469</v>
       </c>
       <c r="B86" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>135384124</v>
       </c>
       <c r="B87" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135356241</v>
       </c>
       <c r="B88" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>135357201</v>
       </c>
       <c r="B89" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135357211</v>
       </c>
       <c r="B90" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>135357212</v>
       </c>
       <c r="B91" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>135358340</v>
       </c>
       <c r="B92" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135358342</v>
       </c>
       <c r="B93" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>135382720</v>
       </c>
       <c r="B94" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135382723</v>
       </c>
       <c r="B95" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135356886</v>
       </c>
       <c r="B96" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>135356243</v>
       </c>
       <c r="B97" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>135356884</v>
       </c>
       <c r="B98" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>135382031</v>
       </c>
       <c r="B99" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>135382032</v>
       </c>
       <c r="B100" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>135384245</v>
       </c>
       <c r="B101" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>135384249</v>
       </c>
       <c r="B102" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>135382721</v>
       </c>
       <c r="B103" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>135384251</v>
       </c>
       <c r="B104" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>135357209</v>
       </c>
       <c r="B105" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>135357202</v>
       </c>
       <c r="B106" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>135382724</v>
       </c>
       <c r="B107" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>135357195</v>
       </c>
       <c r="B108" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>135357198</v>
       </c>
       <c r="B109" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>135382718</v>
       </c>
       <c r="B110" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>135357196</v>
       </c>
       <c r="B111" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>135357199</v>
       </c>
       <c r="B112" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>135357205</v>
       </c>
       <c r="B113" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>135357206</v>
       </c>
       <c r="B114" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>135357213</v>
       </c>
       <c r="B115" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>135358341</v>
       </c>
       <c r="B116" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>135382717</v>
       </c>
       <c r="B117" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>135382722</v>
       </c>
       <c r="B118" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>135356859</v>
       </c>
       <c r="B119" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>135353510</v>
       </c>
       <c r="B120" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>135353501</v>
       </c>
       <c r="B121" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>135353508</v>
       </c>
       <c r="B122" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>135353519</v>
       </c>
       <c r="B123" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>135353522</v>
       </c>
       <c r="B124" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>135353525</v>
       </c>
       <c r="B125" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>135356379</v>
       </c>
       <c r="B126" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>135356849</v>
       </c>
       <c r="B127" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>135356851</v>
       </c>
       <c r="B128" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>135356854</v>
       </c>
       <c r="B129" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>135357135</v>
       </c>
       <c r="B130" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>135358290</v>
       </c>
       <c r="B131" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>135358300</v>
       </c>
       <c r="B132" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>135382781</v>
       </c>
       <c r="B133" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>135353499</v>
       </c>
       <c r="B134" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135353520</v>
       </c>
       <c r="B135" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>135382780</v>
       </c>
       <c r="B136" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>135353502</v>
       </c>
       <c r="B137" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>135356215</v>
       </c>
       <c r="B138" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>135356221</v>
       </c>
       <c r="B139" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>135356847</v>
       </c>
       <c r="B140" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>135358294</v>
       </c>
       <c r="B141" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>135353523</v>
       </c>
       <c r="B142" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>135356220</v>
       </c>
       <c r="B143" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>135356850</v>
       </c>
       <c r="B144" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>135357150</v>
       </c>
       <c r="B145" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>135358297</v>
       </c>
       <c r="B146" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>135358304</v>
       </c>
       <c r="B147" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>135353517</v>
       </c>
       <c r="B148" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>135356378</v>
       </c>
       <c r="B149" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>135356861</v>
       </c>
       <c r="B150" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>135353524</v>
       </c>
       <c r="B151" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>135358288</v>
       </c>
       <c r="B152" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>135358298</v>
       </c>
       <c r="B153" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>135356223</v>
       </c>
       <c r="B154" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>135356224</v>
       </c>
       <c r="B155" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>135356857</v>
       </c>
       <c r="B156" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>135353500</v>
       </c>
       <c r="B157" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>135356853</v>
       </c>
       <c r="B158" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>135357133</v>
       </c>
       <c r="B159" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>135357142</v>
       </c>
       <c r="B160" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>135382782</v>
       </c>
       <c r="B161" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>135356855</v>
       </c>
       <c r="B162" t="n">
-        <v>92806</v>
+        <v>92848</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>135353513</v>
       </c>
       <c r="B163" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>135353515</v>
       </c>
       <c r="B164" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>135353526</v>
       </c>
       <c r="B165" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>135353529</v>
       </c>
       <c r="B166" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>135353534</v>
       </c>
       <c r="B167" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>135362165</v>
       </c>
       <c r="B168" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>135353509</v>
       </c>
       <c r="B169" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>135353530</v>
       </c>
       <c r="B170" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>135353535</v>
       </c>
       <c r="B171" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>135356222</v>
       </c>
       <c r="B172" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>135358306</v>
       </c>
       <c r="B173" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>135358308</v>
       </c>
       <c r="B174" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>135353531</v>
       </c>
       <c r="B175" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>135353533</v>
       </c>
       <c r="B176" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>135356216</v>
       </c>
       <c r="B177" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>135356380</v>
       </c>
       <c r="B178" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>135357148</v>
       </c>
       <c r="B179" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>135357151</v>
       </c>
       <c r="B180" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>135357152</v>
       </c>
       <c r="B181" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>135353537</v>
       </c>
       <c r="B182" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135361173</v>
       </c>
       <c r="B183" t="n">
-        <v>110023</v>
+        <v>110079</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>135353512</v>
       </c>
       <c r="B184" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>135353528</v>
       </c>
       <c r="B185" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>135357137</v>
       </c>
       <c r="B186" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>135357141</v>
       </c>
       <c r="B187" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>135358292</v>
       </c>
       <c r="B188" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>135358295</v>
       </c>
       <c r="B189" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>135358307</v>
       </c>
       <c r="B190" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>135356218</v>
       </c>
       <c r="B191" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>135358287</v>
       </c>
       <c r="B192" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>135353521</v>
       </c>
       <c r="B193" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>135353527</v>
       </c>
       <c r="B194" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>135356856</v>
       </c>
       <c r="B195" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>135356858</v>
       </c>
       <c r="B196" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>135356860</v>
       </c>
       <c r="B197" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>135356862</v>
       </c>
       <c r="B198" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>135362163</v>
       </c>
       <c r="B199" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>135357136</v>
       </c>
       <c r="B200" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135357146</v>
       </c>
       <c r="B201" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>135357145</v>
       </c>
       <c r="B202" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>135358296</v>
       </c>
       <c r="B203" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>135357138</v>
       </c>
       <c r="B204" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>135357140</v>
       </c>
       <c r="B205" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>135357147</v>
       </c>
       <c r="B206" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>135358293</v>
       </c>
       <c r="B207" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>135358302</v>
       </c>
       <c r="B208" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135358310</v>
       </c>
       <c r="B209" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>135356852</v>
       </c>
       <c r="B210" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>135357134</v>
       </c>
       <c r="B211" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>135353573</v>
       </c>
       <c r="B214" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>135350748</v>
       </c>
       <c r="B217" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>135353572</v>
       </c>
       <c r="B218" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>135357173</v>
       </c>
       <c r="B219" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>135357185</v>
       </c>
       <c r="B224" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>135357176</v>
       </c>
       <c r="B226" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>135353574</v>
       </c>
       <c r="B229" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>135356234</v>
       </c>
       <c r="B230" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>135356383</v>
       </c>
       <c r="B231" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>135357168</v>
       </c>
       <c r="B232" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>135362174</v>
       </c>
       <c r="B233" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>135362172</v>
       </c>
       <c r="B234" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>135356382</v>
       </c>
       <c r="B235" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>135358333</v>
       </c>
       <c r="B236" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>135356235</v>
       </c>
       <c r="B237" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28095,7 +28095,7 @@
         <v>135357184</v>
       </c>
       <c r="B238" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>135356384</v>
       </c>
       <c r="B239" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>135356879</v>
       </c>
       <c r="B240" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>135356880</v>
       </c>
       <c r="B241" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>135382462</v>
       </c>
       <c r="B242" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>135356881</v>
       </c>
       <c r="B243" t="n">
-        <v>99094</v>
+        <v>99141</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>135357170</v>
       </c>
       <c r="B244" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>135357172</v>
       </c>
       <c r="B245" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>135357187</v>
       </c>
       <c r="B246" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>135353575</v>
       </c>
       <c r="B248" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>135357179</v>
       </c>
       <c r="B249" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>135358332</v>
       </c>
       <c r="B250" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>135353577</v>
       </c>
       <c r="B251" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>135356877</v>
       </c>
       <c r="B252" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>135357180</v>
       </c>
       <c r="B253" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>135357193</v>
       </c>
       <c r="B254" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>135362173</v>
       </c>
       <c r="B255" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>135383915</v>
       </c>
       <c r="B256" t="n">
-        <v>99205</v>
+        <v>99252</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>135357178</v>
       </c>
       <c r="B257" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>135357190</v>
       </c>
       <c r="B258" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>135357169</v>
       </c>
       <c r="B259" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>135357177</v>
       </c>
       <c r="B260" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>135357182</v>
       </c>
       <c r="B261" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>135357183</v>
       </c>
       <c r="B262" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>135357186</v>
       </c>
       <c r="B263" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>135357188</v>
       </c>
       <c r="B264" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>135357191</v>
       </c>
       <c r="B265" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>135353538</v>
       </c>
       <c r="B266" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>135356867</v>
       </c>
       <c r="B267" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>135353549</v>
       </c>
       <c r="B268" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>135356231</v>
       </c>
       <c r="B269" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>135356870</v>
       </c>
       <c r="B270" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>135353541</v>
       </c>
       <c r="B271" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>135356227</v>
       </c>
       <c r="B272" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>135356228</v>
       </c>
       <c r="B273" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>135353539</v>
       </c>
       <c r="B274" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>135353545</v>
       </c>
       <c r="B275" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>135356865</v>
       </c>
       <c r="B276" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>135353540</v>
       </c>
       <c r="B277" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>135356868</v>
       </c>
       <c r="B278" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>135356869</v>
       </c>
       <c r="B279" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>135353547</v>
       </c>
       <c r="B280" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>135356230</v>
       </c>
       <c r="B281" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>135353543</v>
       </c>
       <c r="B282" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>135356871</v>
       </c>
       <c r="B283" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>135356863</v>
       </c>
       <c r="B284" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>135353546</v>
       </c>
       <c r="B285" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>135353551</v>
       </c>
       <c r="B286" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>135356226</v>
       </c>
       <c r="B287" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>135356229</v>
       </c>
       <c r="B288" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>135356864</v>
       </c>
       <c r="B289" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>135358313</v>
       </c>
       <c r="B290" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>135353550</v>
       </c>
       <c r="B291" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>135356866</v>
       </c>
       <c r="B292" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>135357158</v>
       </c>
       <c r="B293" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135357166</v>
       </c>
       <c r="B294" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>135358328</v>
       </c>
       <c r="B295" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>135358316</v>
       </c>
       <c r="B296" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>135358324</v>
       </c>
       <c r="B297" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>135357161</v>
       </c>
       <c r="B298" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>135357162</v>
       </c>
       <c r="B299" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>135357164</v>
       </c>
       <c r="B300" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>135358318</v>
       </c>
       <c r="B301" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>135358327</v>
       </c>
       <c r="B302" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>135357167</v>
       </c>
       <c r="B303" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>135357160</v>
       </c>
       <c r="B304" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>135358317</v>
       </c>
       <c r="B305" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>135353570</v>
       </c>
       <c r="B306" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>135358321</v>
       </c>
       <c r="B307" t="n">
-        <v>96037</v>
+        <v>96081</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>135354303</v>
       </c>
       <c r="B308" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>135356874</v>
       </c>
       <c r="B309" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>135353564</v>
       </c>
       <c r="B310" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>135353563</v>
       </c>
       <c r="B311" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>135353567</v>
       </c>
       <c r="B312" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>135353571</v>
       </c>
       <c r="B313" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>135356381</v>
       </c>
       <c r="B314" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37056,7 +37056,7 @@
         <v>135357157</v>
       </c>
       <c r="B315" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>135353553</v>
       </c>
       <c r="B316" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37306,7 +37306,7 @@
         <v>135357159</v>
       </c>
       <c r="B317" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>135356873</v>
       </c>
       <c r="B318" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>135353565</v>
       </c>
       <c r="B319" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>135353568</v>
       </c>
       <c r="B320" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>135356875</v>
       </c>
       <c r="B321" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>135357165</v>
       </c>
       <c r="B322" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>135358325</v>
       </c>
       <c r="B323" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>135358329</v>
       </c>
       <c r="B324" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>135362167</v>
       </c>
       <c r="B325" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>135357153</v>
       </c>
       <c r="B326" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>135357154</v>
       </c>
       <c r="B327" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>135358315</v>
       </c>
       <c r="B328" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>135358323</v>
       </c>
       <c r="B329" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>135358330</v>
       </c>
       <c r="B330" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>135351898</v>
       </c>
       <c r="B331" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>135353558</v>
       </c>
       <c r="B332" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>135353557</v>
       </c>
       <c r="B333" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>135353560</v>
       </c>
       <c r="B334" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>135353561</v>
       </c>
       <c r="B335" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>135353555</v>
       </c>
       <c r="B336" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>135350679</v>
       </c>
       <c r="B337" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>135350592</v>
       </c>
       <c r="B338" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>135350677</v>
       </c>
       <c r="B339" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>135350680</v>
       </c>
       <c r="B340" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>135350590</v>
       </c>
       <c r="B341" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>135350593</v>
       </c>
       <c r="B342" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135356842</v>
       </c>
       <c r="B2" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135356375</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135356889</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135357129</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135353493</v>
       </c>
       <c r="B6" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>135353492</v>
       </c>
       <c r="B7" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>135353498</v>
       </c>
       <c r="B8" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135356848</v>
       </c>
       <c r="B9" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135358272</v>
       </c>
       <c r="B10" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135358273</v>
       </c>
       <c r="B11" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135358280</v>
       </c>
       <c r="B12" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>135356374</v>
       </c>
       <c r="B13" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135382715</v>
       </c>
       <c r="B14" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>135382714</v>
       </c>
       <c r="B15" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135356212</v>
       </c>
       <c r="B16" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135420258</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92896</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>135356208</v>
       </c>
       <c r="B18" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135357125</v>
       </c>
       <c r="B19" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135357124</v>
       </c>
       <c r="B20" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135356210</v>
       </c>
       <c r="B21" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135356372</v>
       </c>
       <c r="B22" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>135353495</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>135356837</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         <v>135356841</v>
       </c>
       <c r="B25" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>135357126</v>
       </c>
       <c r="B26" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>135384162</v>
       </c>
       <c r="B33" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>135356843</v>
       </c>
       <c r="B34" t="n">
-        <v>99146</v>
+        <v>99173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135358269</v>
       </c>
       <c r="B35" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135353491</v>
       </c>
       <c r="B36" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>135356209</v>
       </c>
       <c r="B37" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135356839</v>
       </c>
       <c r="B38" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135358270</v>
       </c>
       <c r="B39" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135356206</v>
       </c>
       <c r="B40" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>135356845</v>
       </c>
       <c r="B41" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>135358281</v>
       </c>
       <c r="B42" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>135353486</v>
       </c>
       <c r="B43" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>135353494</v>
       </c>
       <c r="B44" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>135353497</v>
       </c>
       <c r="B45" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>135356211</v>
       </c>
       <c r="B46" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>135356213</v>
       </c>
       <c r="B47" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>135356844</v>
       </c>
       <c r="B48" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>135356846</v>
       </c>
       <c r="B49" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135353490</v>
       </c>
       <c r="B50" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>135362160</v>
       </c>
       <c r="B51" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>135358271</v>
       </c>
       <c r="B52" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>135356838</v>
       </c>
       <c r="B53" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>135357123</v>
       </c>
       <c r="B54" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>135382713</v>
       </c>
       <c r="B55" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>135357122</v>
       </c>
       <c r="B56" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135357120</v>
       </c>
       <c r="B57" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>135358268</v>
       </c>
       <c r="B58" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>135358284</v>
       </c>
       <c r="B59" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>135382388</v>
       </c>
       <c r="B60" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>135382712</v>
       </c>
       <c r="B61" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>135357130</v>
       </c>
       <c r="B62" t="n">
-        <v>102000</v>
+        <v>102027</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>135356244</v>
       </c>
       <c r="B63" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>135356883</v>
       </c>
       <c r="B64" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>135356888</v>
       </c>
       <c r="B65" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>135356887</v>
       </c>
       <c r="B66" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135356242</v>
       </c>
       <c r="B67" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>135357194</v>
       </c>
       <c r="B68" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135379282</v>
       </c>
       <c r="B69" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135379283</v>
       </c>
       <c r="B70" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>135385142</v>
       </c>
       <c r="B71" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>135356239</v>
       </c>
       <c r="B72" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>135357197</v>
       </c>
       <c r="B73" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>135357203</v>
       </c>
       <c r="B74" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135357207</v>
       </c>
       <c r="B75" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>135357208</v>
       </c>
       <c r="B76" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>135382719</v>
       </c>
       <c r="B77" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>135356240</v>
       </c>
       <c r="B78" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>135382464</v>
       </c>
       <c r="B79" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>135382466</v>
       </c>
       <c r="B80" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>135384252</v>
       </c>
       <c r="B81" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>135382469</v>
       </c>
       <c r="B86" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>135384124</v>
       </c>
       <c r="B87" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135356241</v>
       </c>
       <c r="B88" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>135357201</v>
       </c>
       <c r="B89" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135357211</v>
       </c>
       <c r="B90" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>135357212</v>
       </c>
       <c r="B91" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>135358340</v>
       </c>
       <c r="B92" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135358342</v>
       </c>
       <c r="B93" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>135382720</v>
       </c>
       <c r="B94" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135382723</v>
       </c>
       <c r="B95" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135356886</v>
       </c>
       <c r="B96" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>135356243</v>
       </c>
       <c r="B97" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>135356884</v>
       </c>
       <c r="B98" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>135382031</v>
       </c>
       <c r="B99" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>135382032</v>
       </c>
       <c r="B100" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>135384245</v>
       </c>
       <c r="B101" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>135384249</v>
       </c>
       <c r="B102" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>135382721</v>
       </c>
       <c r="B103" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>135384251</v>
       </c>
       <c r="B104" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>135357209</v>
       </c>
       <c r="B105" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>135357202</v>
       </c>
       <c r="B106" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>135382724</v>
       </c>
       <c r="B107" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>135357195</v>
       </c>
       <c r="B108" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>135357198</v>
       </c>
       <c r="B109" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>135382718</v>
       </c>
       <c r="B110" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>135357196</v>
       </c>
       <c r="B111" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>135357199</v>
       </c>
       <c r="B112" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>135357205</v>
       </c>
       <c r="B113" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>135357206</v>
       </c>
       <c r="B114" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>135357213</v>
       </c>
       <c r="B115" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>135358341</v>
       </c>
       <c r="B116" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>135382717</v>
       </c>
       <c r="B117" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>135382722</v>
       </c>
       <c r="B118" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>135356859</v>
       </c>
       <c r="B119" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>135353510</v>
       </c>
       <c r="B120" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>135353501</v>
       </c>
       <c r="B121" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>135353508</v>
       </c>
       <c r="B122" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>135353519</v>
       </c>
       <c r="B123" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>135353522</v>
       </c>
       <c r="B124" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>135353525</v>
       </c>
       <c r="B125" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>135356379</v>
       </c>
       <c r="B126" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>135356849</v>
       </c>
       <c r="B127" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>135356851</v>
       </c>
       <c r="B128" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>135356854</v>
       </c>
       <c r="B129" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>135357135</v>
       </c>
       <c r="B130" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>135358290</v>
       </c>
       <c r="B131" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>135358300</v>
       </c>
       <c r="B132" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>135382781</v>
       </c>
       <c r="B133" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>135353499</v>
       </c>
       <c r="B134" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135353520</v>
       </c>
       <c r="B135" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>135382780</v>
       </c>
       <c r="B136" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>135353502</v>
       </c>
       <c r="B137" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>135356215</v>
       </c>
       <c r="B138" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>135356221</v>
       </c>
       <c r="B139" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>135356847</v>
       </c>
       <c r="B140" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>135358294</v>
       </c>
       <c r="B141" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>135353523</v>
       </c>
       <c r="B142" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>135356220</v>
       </c>
       <c r="B143" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>135356850</v>
       </c>
       <c r="B144" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>135357150</v>
       </c>
       <c r="B145" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>135358297</v>
       </c>
       <c r="B146" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>135358304</v>
       </c>
       <c r="B147" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>135353517</v>
       </c>
       <c r="B148" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>135356378</v>
       </c>
       <c r="B149" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>135356861</v>
       </c>
       <c r="B150" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>135353524</v>
       </c>
       <c r="B151" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>135358288</v>
       </c>
       <c r="B152" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>135358298</v>
       </c>
       <c r="B153" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>135356223</v>
       </c>
       <c r="B154" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>135356224</v>
       </c>
       <c r="B155" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>135356857</v>
       </c>
       <c r="B156" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>135353500</v>
       </c>
       <c r="B157" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>135356853</v>
       </c>
       <c r="B158" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>135357133</v>
       </c>
       <c r="B159" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>135357142</v>
       </c>
       <c r="B160" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>135382782</v>
       </c>
       <c r="B161" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>135356855</v>
       </c>
       <c r="B162" t="n">
-        <v>92848</v>
+        <v>92875</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>135353513</v>
       </c>
       <c r="B163" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>135353515</v>
       </c>
       <c r="B164" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>135353526</v>
       </c>
       <c r="B165" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>135353529</v>
       </c>
       <c r="B166" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>135353534</v>
       </c>
       <c r="B167" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>135362165</v>
       </c>
       <c r="B168" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>135353509</v>
       </c>
       <c r="B169" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>135353530</v>
       </c>
       <c r="B170" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>135353535</v>
       </c>
       <c r="B171" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>135356222</v>
       </c>
       <c r="B172" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>135358306</v>
       </c>
       <c r="B173" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>135358308</v>
       </c>
       <c r="B174" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>135353537</v>
       </c>
       <c r="B182" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135361173</v>
       </c>
       <c r="B183" t="n">
-        <v>110079</v>
+        <v>110106</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>135353512</v>
       </c>
       <c r="B184" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>135353528</v>
       </c>
       <c r="B185" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>135357137</v>
       </c>
       <c r="B186" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>135357141</v>
       </c>
       <c r="B187" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>135358292</v>
       </c>
       <c r="B188" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>135358295</v>
       </c>
       <c r="B189" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>135358307</v>
       </c>
       <c r="B190" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>135356218</v>
       </c>
       <c r="B191" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>135358287</v>
       </c>
       <c r="B192" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>135353521</v>
       </c>
       <c r="B193" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>135353527</v>
       </c>
       <c r="B194" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>135356856</v>
       </c>
       <c r="B195" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>135356858</v>
       </c>
       <c r="B196" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>135356860</v>
       </c>
       <c r="B197" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>135356862</v>
       </c>
       <c r="B198" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>135362163</v>
       </c>
       <c r="B199" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>135357136</v>
       </c>
       <c r="B200" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135357146</v>
       </c>
       <c r="B201" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>135357145</v>
       </c>
       <c r="B202" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>135358296</v>
       </c>
       <c r="B203" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>135357138</v>
       </c>
       <c r="B204" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>135357140</v>
       </c>
       <c r="B205" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>135357147</v>
       </c>
       <c r="B206" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>135358293</v>
       </c>
       <c r="B207" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>135358302</v>
       </c>
       <c r="B208" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135358310</v>
       </c>
       <c r="B209" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>135356852</v>
       </c>
       <c r="B210" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>135357134</v>
       </c>
       <c r="B211" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>135353573</v>
       </c>
       <c r="B214" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>135350748</v>
       </c>
       <c r="B217" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>135353572</v>
       </c>
       <c r="B218" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>135357173</v>
       </c>
       <c r="B219" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>135357185</v>
       </c>
       <c r="B224" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>135357176</v>
       </c>
       <c r="B226" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>135353574</v>
       </c>
       <c r="B229" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>135356234</v>
       </c>
       <c r="B230" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>135356383</v>
       </c>
       <c r="B231" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>135357168</v>
       </c>
       <c r="B232" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>135362174</v>
       </c>
       <c r="B233" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>135362172</v>
       </c>
       <c r="B234" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>135356384</v>
       </c>
       <c r="B239" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>135356879</v>
       </c>
       <c r="B240" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>135356880</v>
       </c>
       <c r="B241" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>135382462</v>
       </c>
       <c r="B242" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>135356881</v>
       </c>
       <c r="B243" t="n">
-        <v>99141</v>
+        <v>99168</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>135357170</v>
       </c>
       <c r="B244" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>135357172</v>
       </c>
       <c r="B245" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>135357187</v>
       </c>
       <c r="B246" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>135353575</v>
       </c>
       <c r="B248" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>135357179</v>
       </c>
       <c r="B249" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>135358332</v>
       </c>
       <c r="B250" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>135353577</v>
       </c>
       <c r="B251" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>135356877</v>
       </c>
       <c r="B252" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>135357180</v>
       </c>
       <c r="B253" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>135357193</v>
       </c>
       <c r="B254" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>135362173</v>
       </c>
       <c r="B255" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>135383915</v>
       </c>
       <c r="B256" t="n">
-        <v>99252</v>
+        <v>99279</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>135357178</v>
       </c>
       <c r="B257" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>135357190</v>
       </c>
       <c r="B258" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>135357169</v>
       </c>
       <c r="B259" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>135357177</v>
       </c>
       <c r="B260" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>135357182</v>
       </c>
       <c r="B261" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>135357183</v>
       </c>
       <c r="B262" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>135357186</v>
       </c>
       <c r="B263" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>135357188</v>
       </c>
       <c r="B264" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>135357191</v>
       </c>
       <c r="B265" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>135353538</v>
       </c>
       <c r="B266" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>135356867</v>
       </c>
       <c r="B267" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>135353549</v>
       </c>
       <c r="B268" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>135356231</v>
       </c>
       <c r="B269" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>135356870</v>
       </c>
       <c r="B270" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>135353541</v>
       </c>
       <c r="B271" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>135356227</v>
       </c>
       <c r="B272" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>135356228</v>
       </c>
       <c r="B273" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>135353539</v>
       </c>
       <c r="B274" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>135353545</v>
       </c>
       <c r="B275" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>135356865</v>
       </c>
       <c r="B276" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>135353540</v>
       </c>
       <c r="B277" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>135356868</v>
       </c>
       <c r="B278" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>135356869</v>
       </c>
       <c r="B279" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>135353543</v>
       </c>
       <c r="B282" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>135356871</v>
       </c>
       <c r="B283" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>135356863</v>
       </c>
       <c r="B284" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>135353546</v>
       </c>
       <c r="B285" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>135353551</v>
       </c>
       <c r="B286" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>135356226</v>
       </c>
       <c r="B287" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>135356229</v>
       </c>
       <c r="B288" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>135356864</v>
       </c>
       <c r="B289" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>135358313</v>
       </c>
       <c r="B290" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>135353550</v>
       </c>
       <c r="B291" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>135356866</v>
       </c>
       <c r="B292" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>135357158</v>
       </c>
       <c r="B293" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135357166</v>
       </c>
       <c r="B294" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>135358328</v>
       </c>
       <c r="B295" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>135358316</v>
       </c>
       <c r="B296" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>135358324</v>
       </c>
       <c r="B297" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>135357161</v>
       </c>
       <c r="B298" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>135357162</v>
       </c>
       <c r="B299" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>135357164</v>
       </c>
       <c r="B300" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>135358318</v>
       </c>
       <c r="B301" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>135358327</v>
       </c>
       <c r="B302" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>135357167</v>
       </c>
       <c r="B303" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>135357160</v>
       </c>
       <c r="B304" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>135358317</v>
       </c>
       <c r="B305" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>135353570</v>
       </c>
       <c r="B306" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>135358321</v>
       </c>
       <c r="B307" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>135354303</v>
       </c>
       <c r="B308" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>135356874</v>
       </c>
       <c r="B309" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>135353564</v>
       </c>
       <c r="B310" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>135356873</v>
       </c>
       <c r="B318" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>135353565</v>
       </c>
       <c r="B319" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>135353568</v>
       </c>
       <c r="B320" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>135356875</v>
       </c>
       <c r="B321" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>135357165</v>
       </c>
       <c r="B322" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>135358325</v>
       </c>
       <c r="B323" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>135358329</v>
       </c>
       <c r="B324" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>135362167</v>
       </c>
       <c r="B325" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>135357153</v>
       </c>
       <c r="B326" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>135357154</v>
       </c>
       <c r="B327" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>135358315</v>
       </c>
       <c r="B328" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>135358323</v>
       </c>
       <c r="B329" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>135358330</v>
       </c>
       <c r="B330" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>135351898</v>
       </c>
       <c r="B331" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>135353558</v>
       </c>
       <c r="B332" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>135353555</v>
       </c>
       <c r="B336" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39644,7 +39644,7 @@
         <v>135350679</v>
       </c>
       <c r="B337" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>135350592</v>
       </c>
       <c r="B338" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>135350677</v>
       </c>
       <c r="B339" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>135350680</v>
       </c>
       <c r="B340" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>135350590</v>
       </c>
       <c r="B341" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>135350593</v>
       </c>
       <c r="B342" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -39741,7 +39741,7 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -39973,7 +39973,7 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, per-erik mukka, Helena Björnström, Jörgen Sundin, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -40089,7 +40089,7 @@
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -39741,7 +39741,7 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -39973,7 +39973,7 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, per-erik mukka, Helena Björnström, Jörgen Sundin, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -40089,7 +40089,7 @@
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Marie Persson, Elin Kannerby, Lina Hällström, Christina Boyd, Amanda Wiker Briceño, Agne Jonsson, Laura Dobrandt, Moa Turid Lövdahl, per-erik mukka, Helena Björnström, Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Helena Björnström, per-erik mukka, Moa Turid Lövdahl, Laura Dobrandt, Agne Jonsson, Amanda Wiker Briceño, Christina Boyd, Lina Hällström, Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>135356375</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135356889</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>135357129</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>135353493</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>135353492</v>
       </c>
       <c r="B7" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>135353498</v>
       </c>
       <c r="B8" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135356848</v>
       </c>
       <c r="B9" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135358272</v>
       </c>
       <c r="B10" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135358273</v>
       </c>
       <c r="B11" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135358280</v>
       </c>
       <c r="B12" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>135356374</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135382715</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>135382714</v>
       </c>
       <c r="B15" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135356212</v>
       </c>
       <c r="B16" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135420258</v>
       </c>
       <c r="B17" t="n">
-        <v>92901</v>
+        <v>92903</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>135356208</v>
       </c>
       <c r="B18" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>135357124</v>
       </c>
       <c r="B20" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>135356210</v>
       </c>
       <c r="B21" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>135356372</v>
       </c>
       <c r="B22" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>135384162</v>
       </c>
       <c r="B33" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>135356843</v>
       </c>
       <c r="B34" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135358269</v>
       </c>
       <c r="B35" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135353491</v>
       </c>
       <c r="B36" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>135356209</v>
       </c>
       <c r="B37" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135356839</v>
       </c>
       <c r="B38" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>135358270</v>
       </c>
       <c r="B39" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>135356206</v>
       </c>
       <c r="B40" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>135356845</v>
       </c>
       <c r="B41" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>135358281</v>
       </c>
       <c r="B42" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>135353486</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>135353494</v>
       </c>
       <c r="B44" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>135353497</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>135356211</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>135356213</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>135356844</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>135356846</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>135353490</v>
       </c>
       <c r="B50" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>135362160</v>
       </c>
       <c r="B51" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>135358271</v>
       </c>
       <c r="B52" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>135356838</v>
       </c>
       <c r="B53" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>135357123</v>
       </c>
       <c r="B54" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>135382713</v>
       </c>
       <c r="B55" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>135357122</v>
       </c>
       <c r="B56" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135357120</v>
       </c>
       <c r="B57" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>135358268</v>
       </c>
       <c r="B58" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>135358284</v>
       </c>
       <c r="B59" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>135382388</v>
       </c>
       <c r="B60" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         <v>135382712</v>
       </c>
       <c r="B61" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>135357130</v>
       </c>
       <c r="B62" t="n">
-        <v>102032</v>
+        <v>102034</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>135356244</v>
       </c>
       <c r="B63" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         <v>135356883</v>
       </c>
       <c r="B64" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>135356888</v>
       </c>
       <c r="B65" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>135356887</v>
       </c>
       <c r="B66" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>135356242</v>
       </c>
       <c r="B67" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>135357194</v>
       </c>
       <c r="B68" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>135379282</v>
       </c>
       <c r="B69" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135379283</v>
       </c>
       <c r="B70" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>135385142</v>
       </c>
       <c r="B71" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>135356239</v>
       </c>
       <c r="B72" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>135357197</v>
       </c>
       <c r="B73" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>135357203</v>
       </c>
       <c r="B74" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135357207</v>
       </c>
       <c r="B75" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>135357208</v>
       </c>
       <c r="B76" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>135382719</v>
       </c>
       <c r="B77" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>135382469</v>
       </c>
       <c r="B86" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>135384124</v>
       </c>
       <c r="B87" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135356241</v>
       </c>
       <c r="B88" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>135357201</v>
       </c>
       <c r="B89" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135357211</v>
       </c>
       <c r="B90" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>135357212</v>
       </c>
       <c r="B91" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>135358340</v>
       </c>
       <c r="B92" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>135358342</v>
       </c>
       <c r="B93" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>135382720</v>
       </c>
       <c r="B94" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135382723</v>
       </c>
       <c r="B95" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>135356886</v>
       </c>
       <c r="B96" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>135356243</v>
       </c>
       <c r="B97" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>135356884</v>
       </c>
       <c r="B98" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>135382031</v>
       </c>
       <c r="B99" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>135382032</v>
       </c>
       <c r="B100" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>135384245</v>
       </c>
       <c r="B101" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>135384249</v>
       </c>
       <c r="B102" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>135382721</v>
       </c>
       <c r="B103" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>135384251</v>
       </c>
       <c r="B104" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>135357209</v>
       </c>
       <c r="B105" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>135357202</v>
       </c>
       <c r="B106" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>135382724</v>
       </c>
       <c r="B107" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>135357195</v>
       </c>
       <c r="B108" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>135357198</v>
       </c>
       <c r="B109" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>135382718</v>
       </c>
       <c r="B110" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>135357196</v>
       </c>
       <c r="B111" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>135357199</v>
       </c>
       <c r="B112" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>135357205</v>
       </c>
       <c r="B113" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>135357206</v>
       </c>
       <c r="B114" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>135357213</v>
       </c>
       <c r="B115" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>135358341</v>
       </c>
       <c r="B116" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>135382717</v>
       </c>
       <c r="B117" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>135382722</v>
       </c>
       <c r="B118" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>135353501</v>
       </c>
       <c r="B121" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>135353508</v>
       </c>
       <c r="B122" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>135353519</v>
       </c>
       <c r="B123" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>135353522</v>
       </c>
       <c r="B124" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>135353525</v>
       </c>
       <c r="B125" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>135356379</v>
       </c>
       <c r="B126" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>135356849</v>
       </c>
       <c r="B127" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>135356851</v>
       </c>
       <c r="B128" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>135356854</v>
       </c>
       <c r="B129" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>135357135</v>
       </c>
       <c r="B130" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>135358290</v>
       </c>
       <c r="B131" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
         <v>135358300</v>
       </c>
       <c r="B132" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>135382781</v>
       </c>
       <c r="B133" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>135353499</v>
       </c>
       <c r="B134" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>135353520</v>
       </c>
       <c r="B135" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>135382780</v>
       </c>
       <c r="B136" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>135353502</v>
       </c>
       <c r="B137" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>135356215</v>
       </c>
       <c r="B138" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>135356221</v>
       </c>
       <c r="B139" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>135356847</v>
       </c>
       <c r="B140" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>135358294</v>
       </c>
       <c r="B141" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>135353523</v>
       </c>
       <c r="B142" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>135356220</v>
       </c>
       <c r="B143" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>135356850</v>
       </c>
       <c r="B144" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>135357150</v>
       </c>
       <c r="B145" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>135358297</v>
       </c>
       <c r="B146" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>135358304</v>
       </c>
       <c r="B147" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>135353517</v>
       </c>
       <c r="B148" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>135356378</v>
       </c>
       <c r="B149" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>135356861</v>
       </c>
       <c r="B150" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>135353524</v>
       </c>
       <c r="B151" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>135358288</v>
       </c>
       <c r="B152" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>135358298</v>
       </c>
       <c r="B153" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>135353500</v>
       </c>
       <c r="B157" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>135356853</v>
       </c>
       <c r="B158" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>135357133</v>
       </c>
       <c r="B159" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>135357142</v>
       </c>
       <c r="B160" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>135382782</v>
       </c>
       <c r="B161" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>135356855</v>
       </c>
       <c r="B162" t="n">
-        <v>92880</v>
+        <v>92882</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>135353513</v>
       </c>
       <c r="B163" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>135353537</v>
       </c>
       <c r="B182" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135361173</v>
       </c>
       <c r="B183" t="n">
-        <v>110111</v>
+        <v>110113</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>135353512</v>
       </c>
       <c r="B184" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>135353528</v>
       </c>
       <c r="B185" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>135357137</v>
       </c>
       <c r="B186" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>135357141</v>
       </c>
       <c r="B187" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>135358292</v>
       </c>
       <c r="B188" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>135358295</v>
       </c>
       <c r="B189" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>135358307</v>
       </c>
       <c r="B190" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>135356218</v>
       </c>
       <c r="B191" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>135358287</v>
       </c>
       <c r="B192" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>135353521</v>
       </c>
       <c r="B193" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>135353527</v>
       </c>
       <c r="B194" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>135356856</v>
       </c>
       <c r="B195" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>135356858</v>
       </c>
       <c r="B196" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>135356860</v>
       </c>
       <c r="B197" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>135356862</v>
       </c>
       <c r="B198" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>135362163</v>
       </c>
       <c r="B199" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>135357136</v>
       </c>
       <c r="B200" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>135357146</v>
       </c>
       <c r="B201" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>135357145</v>
       </c>
       <c r="B202" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>135358296</v>
       </c>
       <c r="B203" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>135357138</v>
       </c>
       <c r="B204" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>135357140</v>
       </c>
       <c r="B205" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>135357147</v>
       </c>
       <c r="B206" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>135358293</v>
       </c>
       <c r="B207" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>135358302</v>
       </c>
       <c r="B208" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>135358310</v>
       </c>
       <c r="B209" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>135356852</v>
       </c>
       <c r="B210" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>135357134</v>
       </c>
       <c r="B211" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>135353573</v>
       </c>
       <c r="B214" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>135350748</v>
       </c>
       <c r="B217" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>135353572</v>
       </c>
       <c r="B218" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>135357173</v>
       </c>
       <c r="B219" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>135357185</v>
       </c>
       <c r="B224" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>135357176</v>
       </c>
       <c r="B226" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>135356384</v>
       </c>
       <c r="B239" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>135356879</v>
       </c>
       <c r="B240" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>135356880</v>
       </c>
       <c r="B241" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>135382462</v>
       </c>
       <c r="B242" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>135356881</v>
       </c>
       <c r="B243" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>135357170</v>
       </c>
       <c r="B244" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>135357172</v>
       </c>
       <c r="B245" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>135357187</v>
       </c>
       <c r="B246" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>135353575</v>
       </c>
       <c r="B248" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>135357179</v>
       </c>
       <c r="B249" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>135358332</v>
       </c>
       <c r="B250" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>135353577</v>
       </c>
       <c r="B251" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>135356877</v>
       </c>
       <c r="B252" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>135357180</v>
       </c>
       <c r="B253" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>135357193</v>
       </c>
       <c r="B254" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         <v>135362173</v>
       </c>
       <c r="B255" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>135383915</v>
       </c>
       <c r="B256" t="n">
-        <v>99284</v>
+        <v>99286</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>135357178</v>
       </c>
       <c r="B257" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30404,7 +30404,7 @@
         <v>135357190</v>
       </c>
       <c r="B258" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>135357169</v>
       </c>
       <c r="B259" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>135357177</v>
       </c>
       <c r="B260" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>135357182</v>
       </c>
       <c r="B261" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>135357183</v>
       </c>
       <c r="B262" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>135357186</v>
       </c>
       <c r="B263" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31100,7 +31100,7 @@
         <v>135357188</v>
       </c>
       <c r="B264" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>135357191</v>
       </c>
       <c r="B265" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>135356867</v>
       </c>
       <c r="B267" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>135353549</v>
       </c>
       <c r="B268" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>135356231</v>
       </c>
       <c r="B269" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>135356870</v>
       </c>
       <c r="B270" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>135353541</v>
       </c>
       <c r="B271" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>135356227</v>
       </c>
       <c r="B272" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>135356228</v>
       </c>
       <c r="B273" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>135353543</v>
       </c>
       <c r="B282" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>135356871</v>
       </c>
       <c r="B283" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>135356863</v>
       </c>
       <c r="B284" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>135353546</v>
       </c>
       <c r="B285" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>135353551</v>
       </c>
       <c r="B286" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>135356226</v>
       </c>
       <c r="B287" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>135356229</v>
       </c>
       <c r="B288" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>135356864</v>
       </c>
       <c r="B289" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>135358313</v>
       </c>
       <c r="B290" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>135357158</v>
       </c>
       <c r="B293" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>135357166</v>
       </c>
       <c r="B294" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>135358328</v>
       </c>
       <c r="B295" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>135358316</v>
       </c>
       <c r="B296" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>135358324</v>
       </c>
       <c r="B297" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35055,7 +35055,7 @@
         <v>135357161</v>
       </c>
       <c r="B298" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35171,7 +35171,7 @@
         <v>135357162</v>
       </c>
       <c r="B299" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>135357164</v>
       </c>
       <c r="B300" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>135358318</v>
       </c>
       <c r="B301" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>135358327</v>
       </c>
       <c r="B302" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>135357167</v>
       </c>
       <c r="B303" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35751,7 +35751,7 @@
         <v>135357160</v>
       </c>
       <c r="B304" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>135353570</v>
       </c>
       <c r="B306" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>135358321</v>
       </c>
       <c r="B307" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>135356873</v>
       </c>
       <c r="B318" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>135353565</v>
       </c>
       <c r="B319" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>135353568</v>
       </c>
       <c r="B320" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>135356875</v>
       </c>
       <c r="B321" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>135357165</v>
       </c>
       <c r="B322" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>135358325</v>
       </c>
       <c r="B323" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>135358329</v>
       </c>
       <c r="B324" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>135362167</v>
       </c>
       <c r="B325" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>135357153</v>
       </c>
       <c r="B326" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>135357154</v>
       </c>
       <c r="B327" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>135358315</v>
       </c>
       <c r="B328" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>135358323</v>
       </c>
       <c r="B329" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39528,7 +39528,7 @@
         <v>135353555</v>
       </c>
       <c r="B336" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>135350590</v>
       </c>
       <c r="B341" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj S artfynd.xlsx
@@ -2425,7 +2425,7 @@
         <v>135420258</v>
       </c>
       <c r="B17" t="n">
-        <v>92903</v>
+        <v>92918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>135357130</v>
       </c>
       <c r="B62" t="n">
-        <v>102034</v>
+        <v>102051</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135361173</v>
       </c>
       <c r="B183" t="n">
-        <v>110113</v>
+        <v>110136</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
